--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>144916500</v>
+        <v>145007500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.23307438901125208</v>
+        <v>0.23322074756531613</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-476844220.32094395</v>
+        <v>-476753220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-26491345.573385775</v>
+        <v>-26486290.017830219</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>104129000</v>
+        <v>104529000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.230404498215353</v>
+        <v>0.2312895715310109</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-347810961.27051902</v>
+        <v>-347410961.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-19322831.181695502</v>
+        <v>-19300608.959473278</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.40338283486870607</v>
+        <v>0.40954135143158704</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-193.753531078332</v>
+        <v>-191.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-10.764085059907334</v>
+        <v>-10.652973948796223</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>145007500</v>
+        <v>164443500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.23322074756531613</v>
+        <v>0.26448036137618441</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-476753220.32094395</v>
+        <v>-457317220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-26486290.017830219</v>
+        <v>-25406512.240052443</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>125575000</v>
+        <v>140659000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.21834684847696578</v>
+        <v>0.24457455194044619</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-449542071.19165206</v>
+        <v>-434458071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-24974559.510647338</v>
+        <v>-24136559.510647338</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>5500000</v>
+        <v>6700000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>5.9847099762398243E-2</v>
+        <v>7.2904648801466951E-2</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-86400861.058193401</v>
+        <v>-85200861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-4800047.8365663001</v>
+        <v>-4733381.1698996332</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>54900400</v>
+        <v>59833000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.22706322739015208</v>
+        <v>0.24746402730098449</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-186884236.953421</v>
+        <v>-181951636.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10382457.608523389</v>
+        <v>-10108424.275190055</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>104529000</v>
+        <v>113905000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.2312895715310109</v>
+        <v>0.25203569005003201</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-347410961.27051902</v>
+        <v>-338034961.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-19300608.959473278</v>
+        <v>-18779720.07058439</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.62204323010220186</v>
+        <v>0.63547828906769221</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-281.32125870725895</v>
+        <v>-271.32125870725895</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-15.628958817069941</v>
+        <v>-15.073403261514386</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.59048030284242969</v>
+        <v>0.64575930991704011</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-162.981099231874</v>
+        <v>-140.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-9.0545055128818888</v>
+        <v>-7.8322832906596664</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.40954135143158704</v>
+        <v>0.6774368219169109</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-191.753531078332</v>
+        <v>-104.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-10.652973948796223</v>
+        <v>-5.8196406154628892</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>117</v>
+        <v>215</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.29354397819940542</v>
+        <v>0.53941842147753982</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-281.57741493344997</v>
+        <v>-183.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-15.643189718524999</v>
+        <v>-10.198745274080554</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>473</v>
+        <v>913</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.63547828906769221</v>
+        <v>1.2266208835492662</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-271.32125870725895</v>
+        <v>168.67874129274105</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-15.073403261514386</v>
+        <v>9.3710411829300586</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.64575930991704011</v>
+        <v>0.65329735633630515</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-140.981099231874</v>
+        <v>-137.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-7.8322832906596664</v>
+        <v>-7.6656166239929995</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.6774368219169109</v>
+        <v>0.84371676911469817</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-104.753531078332</v>
+        <v>-50.753531078332003</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-5.8196406154628892</v>
+        <v>-2.8196406154628892</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.53941842147753982</v>
+        <v>0.61970395397652256</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-183.57741493344997</v>
+        <v>-151.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-10.198745274080554</v>
+        <v>-8.4209674963027759</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>164443500</v>
+        <v>189862500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.26448036137618441</v>
+        <v>0.30536264803282476</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-457317220.32094395</v>
+        <v>-431898220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-25406512.240052443</v>
+        <v>-23994345.573385775</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>140659000</v>
+        <v>155095000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.24457455194044619</v>
+        <v>0.2696755282861637</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-434458071.19165206</v>
+        <v>-420022071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-24136559.510647338</v>
+        <v>-23334559.510647338</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>59833000</v>
+        <v>57407300</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.24746402730098449</v>
+        <v>0.23743154537589303</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-181951636.953421</v>
+        <v>-184377336.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10108424.275190055</v>
+        <v>-10243185.386301167</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>113905000</v>
+        <v>115196000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.25203569005003201</v>
+        <v>0.25489226417631788</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-338034961.27051902</v>
+        <v>-336743961.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18779720.07058439</v>
+        <v>-18707997.848362166</v>
       </c>
     </row>
     <row r="9" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>189862500</v>
+        <v>200351500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.30536264803282476</v>
+        <v>0.32223248180840602</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-431898220.32094395</v>
+        <v>-421409220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-23994345.573385775</v>
+        <v>-23411623.351163551</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>155095000</v>
+        <v>220592000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.2696755282861637</v>
+        <v>0.3835601672246135</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-420022071.19165206</v>
+        <v>-354525071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-23334559.510647338</v>
+        <v>-19695837.288425114</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>6700000</v>
+        <v>40600000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>7.2904648801466951E-2</v>
+        <v>0.44178040915515793</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-85200861.058193401</v>
+        <v>-51300861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-4733381.1698996332</v>
+        <v>-2850047.8365663001</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>57407300</v>
+        <v>70949800</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.23743154537589303</v>
+        <v>0.29344213467817742</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-184377336.953421</v>
+        <v>-170834836.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10243185.386301167</v>
+        <v>-9490824.2751900554</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>115196000</v>
+        <v>137784500</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.25489226417631788</v>
+        <v>0.3048734606531639</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-336743961.27051902</v>
+        <v>-314155461.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18707997.848362166</v>
+        <v>-17453081.181695502</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.65329735633630515</v>
+        <v>0.67591149559410035</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-137.981099231874</v>
+        <v>-128.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-7.6656166239929995</v>
+        <v>-7.1656166239929995</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.84371676911469817</v>
+        <v>0.86219231880334124</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-50.753531078332003</v>
+        <v>-44.753531078332003</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-2.8196406154628892</v>
+        <v>-2.4863072821295558</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.61970395397652256</v>
+        <v>0.62973964553889539</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-151.57741493344997</v>
+        <v>-147.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-8.4209674963027759</v>
+        <v>-8.1987452740805544</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>70949800</v>
+        <v>71249800</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.29344213467817742</v>
+        <v>0.29468290830126664</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-170834836.953421</v>
+        <v>-170534836.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-9490824.2751900554</v>
+        <v>-9474157.6085233893</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.67591149559410035</v>
+        <v>0.68596222415312036</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-128.981099231874</v>
+        <v>-124.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-7.1656166239929995</v>
+        <v>-6.943394401770778</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>200351500</v>
+        <v>208175000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.32223248180840602</v>
+        <v>0.33481529661851755</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-421409220.32094395</v>
+        <v>-413585720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-23411623.351163551</v>
+        <v>-22976984.462274663</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>220592000</v>
+        <v>232537000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.3835601672246135</v>
+        <v>0.40432985151732587</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-354525071.19165206</v>
+        <v>-342580071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-19695837.288425114</v>
+        <v>-19032226.177314002</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>71249800</v>
+        <v>74861000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.29468290830126664</v>
+        <v>0.30961851399359885</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-170534836.953421</v>
+        <v>-166923636.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-9474157.6085233893</v>
+        <v>-9273535.3863011673</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>137784500</v>
+        <v>141734050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.3048734606531639</v>
+        <v>0.31361256393780551</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-314155461.27051902</v>
+        <v>-310205911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-17453081.181695502</v>
+        <v>-17233661.737251058</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>1.2266208835492662</v>
+        <v>1.2306514012389134</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>168.67874129274105</v>
+        <v>171.67874129274105</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>9.3710411829300586</v>
+        <v>9.5377078495967247</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.86219231880334124</v>
+        <v>0.86527157708478175</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-44.753531078332003</v>
+        <v>-43.753531078332003</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-2.4863072821295558</v>
+        <v>-2.430751726574</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.62973964553889539</v>
+        <v>0.63726641421067498</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-147.57741493344997</v>
+        <v>-144.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-8.1987452740805544</v>
+        <v>-8.0320786074138866</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>208175000</v>
+        <v>261845000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.33481529661851755</v>
+        <v>0.42113467680113237</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-413585720.32094395</v>
+        <v>-359915720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-22976984.462274663</v>
+        <v>-19995317.795607999</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>232537000</v>
+        <v>243967000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.40432985151732587</v>
+        <v>0.42420406595564336</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-342580071.19165206</v>
+        <v>-331150071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-19032226.177314002</v>
+        <v>-18397226.177314002</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>40600000</v>
+        <v>41600000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.44178040915515793</v>
+        <v>0.4526617000210485</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-51300861.058193401</v>
+        <v>-50300861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-2850047.8365663001</v>
+        <v>-2794492.2810107446</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>74861000</v>
+        <v>80161800</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.30961851399359885</v>
+        <v>0.33154215673116944</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-166923636.953421</v>
+        <v>-161622836.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-9273535.3863011673</v>
+        <v>-8979046.4974122774</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>141734050</v>
+        <v>154564050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.31361256393780551</v>
+        <v>0.34200129053753259</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-310205911.27051902</v>
+        <v>-297375911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-17233661.737251058</v>
+        <v>-16520883.959473278</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>273</v>
+        <v>470</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.68596222415312036</v>
+        <v>1.1809606056848594</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-124.981099231874</v>
+        <v>72.018900768126002</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-6.943394401770778</v>
+        <v>4.0010500426736666</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.86527157708478175</v>
+        <v>1.1793559217917131</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-43.753531078332003</v>
+        <v>58.246468921667997</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-2.430751726574</v>
+        <v>3.2359149400926666</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.63726641421067498</v>
+        <v>0.77023932741211498</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-144.57741493344997</v>
+        <v>-91.577414933449973</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-8.0320786074138866</v>
+        <v>-5.0876341629694428</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>261845000</v>
+        <v>273601500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.42113467680113237</v>
+        <v>0.44004307615117733</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-359915720.32094395</v>
+        <v>-348159220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-19995317.795607999</v>
+        <v>-19342178.906719107</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>243967000</v>
+        <v>254532000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.42420406595564336</v>
+        <v>0.44257423879386071</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-331150071.19165206</v>
+        <v>-320585071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-18397226.177314002</v>
+        <v>-17810281.732869558</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>41600000</v>
+        <v>42100000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.4526617000210485</v>
+        <v>0.45810234545399381</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-50300861.058193401</v>
+        <v>-49800861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-2794492.2810107446</v>
+        <v>-2766714.5032329666</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>80161800</v>
+        <v>88823800</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.33154215673116944</v>
+        <v>0.36736742714183124</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-161622836.953421</v>
+        <v>-152960836.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-8979046.4974122774</v>
+        <v>-8497824.2751900554</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>154564050</v>
+        <v>165089050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.34200129053753259</v>
+        <v>0.36528978215578101</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-297375911.27051902</v>
+        <v>-286850911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-16520883.959473278</v>
+        <v>-15936161.737251056</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.1809606056848594</v>
+        <v>1.1985493806631444</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>72.018900768126002</v>
+        <v>79.018900768126002</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>4.0010500426736666</v>
+        <v>4.3899389315625559</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>307</v>
+        <v>376</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.77023932741211498</v>
+        <v>0.94335500686304641</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-91.577414933449973</v>
+        <v>-22.577414933449973</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-5.0876341629694428</v>
+        <v>-1.2543008296361096</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>273601500</v>
+        <v>285325500</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.44004307615117733</v>
+        <v>0.45889920458905653</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-348159220.32094395</v>
+        <v>-336435220.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-19342178.906719107</v>
+        <v>-18690845.573385775</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>254532000</v>
+        <v>264882600</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.44257423879386071</v>
+        <v>0.46057161796842316</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-320585071.19165206</v>
+        <v>-310234471.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-17810281.732869558</v>
+        <v>-17235248.399536226</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>42100000</v>
+        <v>43100000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.45810234545399381</v>
+        <v>0.46898363631988438</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-49800861.058193401</v>
+        <v>-48800861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-2766714.5032329666</v>
+        <v>-2711158.9476774111</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>88823800</v>
+        <v>162797400</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.36736742714183124</v>
+        <v>0.67331573275833223</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-152960836.953421</v>
+        <v>-78987236.953420997</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-8497824.2751900554</v>
+        <v>-4388179.8307456113</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>165089050</v>
+        <v>172608050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.36528978215578101</v>
+        <v>0.38192694780686032</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-286850911.27051902</v>
+        <v>-279331911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15936161.737251056</v>
+        <v>-15518439.515028834</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>916</v>
+        <v>1116</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>1.2306514012389134</v>
+        <v>1.4993525805487198</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>171.67874129274105</v>
+        <v>371.67874129274105</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>9.5377078495967247</v>
+        <v>20.648818960707835</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>1.1793559217917131</v>
+        <v>1.1916729549174752</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>58.246468921667997</v>
+        <v>62.246468921667997</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>3.2359149400926666</v>
+        <v>3.4581371623148889</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.94335500686304641</v>
+        <v>1.0085870020184697</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-22.577414933449973</v>
+        <v>3.4225850665500275</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-1.2543008296361096</v>
+        <v>0.19014361480833486</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>264882600</v>
+        <v>265032600</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.46057161796842316</v>
+        <v>0.4608324344308683</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-310234471.19165206</v>
+        <v>-310084471.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-17235248.399536226</v>
+        <v>-17226915.066202894</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +895,19 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>43100000</v>
+        <v>44100000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.46898363631988438</v>
+        <v>0.479864927185775</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-48800861.058193401</v>
+        <v>-47800861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-2711158.9476774111</v>
+        <v>-2655603.3921218556</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>162797400</v>
+        <v>162947400</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.67331573275833223</v>
+        <v>0.67393611956987687</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-78987236.953420997</v>
+        <v>-78837236.953420997</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-4388179.8307456113</v>
+        <v>-4379846.4974122774</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>172608050</v>
+        <v>172808050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.38192694780686032</v>
+        <v>0.38236948446468927</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-279331911.27051902</v>
+        <v>-279131911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15518439.515028834</v>
+        <v>-15507328.403917722</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1025,19 +1025,19 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>477</v>
+        <v>612</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.1985493806631444</v>
+        <v>1.5377614695300721</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>79.018900768126002</v>
+        <v>214.018900768126</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>4.3899389315625559</v>
+        <v>11.889938931562556</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1077,19 +1077,19 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>1.1916729549174752</v>
+        <v>1.2378618291390828</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>62.246468921667997</v>
+        <v>77.246468921667997</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>3.4581371623148889</v>
+        <v>4.2914704956482224</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.0085870020184697</v>
+        <v>1.1214885320951642</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>3.4225850665500275</v>
+        <v>48.422585066550027</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>0.19014361480833486</v>
+        <v>2.6901436148083349</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -843,19 +843,19 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>285325500</v>
+        <v>287678000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.45889920458905653</v>
+        <v>0.46268281446197623</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-336435220.32094395</v>
+        <v>-334082720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18690845.573385775</v>
+        <v>-18560151.128941331</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +869,19 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>265032600</v>
+        <v>268398600</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.4608324344308683</v>
+        <v>0.46668515584813658</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-310084471.19165206</v>
+        <v>-306718471.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-17226915.066202894</v>
+        <v>-17039915.066202894</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -921,19 +921,19 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>162947400</v>
+        <v>200803400</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.67393611956987687</v>
+        <v>0.83050520715542442</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-78837236.953420997</v>
+        <v>-40981236.953420997</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-4379846.4974122774</v>
+        <v>-2276735.3863011664</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +947,19 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>172808050</v>
+        <v>185786050</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.38236948446468927</v>
+        <v>0.41108568819120977</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-279131911.27051902</v>
+        <v>-266153911.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15507328.403917722</v>
+        <v>-14786328.403917722</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +999,19 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>1.4993525805487198</v>
+        <v>1.5020395923418179</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>371.67874129274105</v>
+        <v>373.67874129274105</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>20.648818960707835</v>
+        <v>20.759930071818946</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1103,19 +1103,19 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.1214885320951642</v>
+        <v>1.1239974549857574</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>48.422585066550027</v>
+        <v>49.422585066550027</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>2.6901436148083349</v>
+        <v>2.7456991703638902</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -15,6 +15,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$D$3</definedName>
   </definedNames>
@@ -525,6 +528,3443 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="MASTER"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>DSE Code</v>
+          </cell>
+          <cell r="I5" t="str">
+            <v>SP SELL IN</v>
+          </cell>
+          <cell r="M5" t="str">
+            <v>ACH OSA</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I6">
+            <v>3</v>
+          </cell>
+          <cell r="M6">
+            <v>260000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="M7">
+            <v>3190000</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="M8">
+            <v>233000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="M9">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I10">
+            <v>3</v>
+          </cell>
+          <cell r="M10">
+            <v>1090000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>660000</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>660000</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I16">
+            <v>5</v>
+          </cell>
+          <cell r="M16">
+            <v>3134000</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="M18">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>3322000</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="M26">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="M27">
+            <v>3526000</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="M28">
+            <v>318000</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I30">
+            <v>1</v>
+          </cell>
+          <cell r="M30">
+            <v>470000</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I31">
+            <v>0</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I32">
+            <v>0</v>
+          </cell>
+          <cell r="M32">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I33">
+            <v>0</v>
+          </cell>
+          <cell r="M33">
+            <v>650000</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I34">
+            <v>0</v>
+          </cell>
+          <cell r="M34">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I35">
+            <v>0</v>
+          </cell>
+          <cell r="M35">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I36">
+            <v>0</v>
+          </cell>
+          <cell r="M36">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I37">
+            <v>0</v>
+          </cell>
+          <cell r="M37">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="C38" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I38">
+            <v>0</v>
+          </cell>
+          <cell r="M38">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="C39" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I39">
+            <v>0</v>
+          </cell>
+          <cell r="M39">
+            <v>461500</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I40">
+            <v>0</v>
+          </cell>
+          <cell r="M40">
+            <v>200000</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I41">
+            <v>0</v>
+          </cell>
+          <cell r="M41">
+            <v>500000</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I42">
+            <v>0</v>
+          </cell>
+          <cell r="M42">
+            <v>324900</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I43">
+            <v>0</v>
+          </cell>
+          <cell r="M43">
+            <v>747000</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I44">
+            <v>0</v>
+          </cell>
+          <cell r="M44">
+            <v>425000</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I45">
+            <v>3</v>
+          </cell>
+          <cell r="M45">
+            <v>558000</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I46">
+            <v>0</v>
+          </cell>
+          <cell r="M46">
+            <v>3200000</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I47">
+            <v>0</v>
+          </cell>
+          <cell r="M47">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I48">
+            <v>0</v>
+          </cell>
+          <cell r="M48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I49">
+            <v>3</v>
+          </cell>
+          <cell r="M49">
+            <v>3189200</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I50">
+            <v>0</v>
+          </cell>
+          <cell r="M50">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="C51" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I51">
+            <v>0</v>
+          </cell>
+          <cell r="M51">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="C52" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I52">
+            <v>0</v>
+          </cell>
+          <cell r="M52">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="C53" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I53">
+            <v>0</v>
+          </cell>
+          <cell r="M53">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="C54" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I54">
+            <v>0</v>
+          </cell>
+          <cell r="M54">
+            <v>500000</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="C55" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I55">
+            <v>0</v>
+          </cell>
+          <cell r="M55">
+            <v>432000</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="C56" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I56">
+            <v>0</v>
+          </cell>
+          <cell r="M56">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="C57" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I57">
+            <v>0</v>
+          </cell>
+          <cell r="M57">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="C58" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I58">
+            <v>0</v>
+          </cell>
+          <cell r="M58">
+            <v>3190000</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="C59" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I59">
+            <v>0</v>
+          </cell>
+          <cell r="M59">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="C60" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I60">
+            <v>3</v>
+          </cell>
+          <cell r="M60">
+            <v>692000</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="C61" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I61">
+            <v>0</v>
+          </cell>
+          <cell r="M61">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="C62" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I62">
+            <v>0</v>
+          </cell>
+          <cell r="M62">
+            <v>352800</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="C63" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I63">
+            <v>0</v>
+          </cell>
+          <cell r="M63">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="C64" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I64">
+            <v>0</v>
+          </cell>
+          <cell r="M64">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="C65" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I65">
+            <v>0</v>
+          </cell>
+          <cell r="M65">
+            <v>234000</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="C66" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I66">
+            <v>0</v>
+          </cell>
+          <cell r="M66">
+            <v>2875000</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="C67" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I67">
+            <v>0</v>
+          </cell>
+          <cell r="M67">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="C68" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I68">
+            <v>0</v>
+          </cell>
+          <cell r="M68">
+            <v>500000</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="C69" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I69">
+            <v>0</v>
+          </cell>
+          <cell r="M69">
+            <v>800000</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="C70" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I70">
+            <v>0</v>
+          </cell>
+          <cell r="M70">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="C71" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I71">
+            <v>0</v>
+          </cell>
+          <cell r="M71">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="C72" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I72">
+            <v>2</v>
+          </cell>
+          <cell r="M72">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="C73" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I73">
+            <v>0</v>
+          </cell>
+          <cell r="M73">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="C74" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I74">
+            <v>0</v>
+          </cell>
+          <cell r="M74">
+            <v>313000</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="C75" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I75">
+            <v>0</v>
+          </cell>
+          <cell r="M75">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="C76" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I76">
+            <v>0</v>
+          </cell>
+          <cell r="M76">
+            <v>324900</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="C77" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I77">
+            <v>3</v>
+          </cell>
+          <cell r="M77">
+            <v>422000</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="C78" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I78">
+            <v>0</v>
+          </cell>
+          <cell r="M78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="C79" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I79">
+            <v>0</v>
+          </cell>
+          <cell r="M79">
+            <v>2695000</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="C80" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I80">
+            <v>0</v>
+          </cell>
+          <cell r="M80">
+            <v>234000</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="C81" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I81">
+            <v>0</v>
+          </cell>
+          <cell r="M81">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="C82" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I82">
+            <v>3</v>
+          </cell>
+          <cell r="M82">
+            <v>90000</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="C83" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I83">
+            <v>3</v>
+          </cell>
+          <cell r="M83">
+            <v>325200</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="C84" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I84">
+            <v>0</v>
+          </cell>
+          <cell r="M84">
+            <v>832800</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="C85" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I85">
+            <v>0</v>
+          </cell>
+          <cell r="M85">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I86">
+            <v>0</v>
+          </cell>
+          <cell r="M86">
+            <v>3164000</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="C87" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I87">
+            <v>0</v>
+          </cell>
+          <cell r="M87">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="C88" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I88">
+            <v>0</v>
+          </cell>
+          <cell r="M88">
+            <v>838000</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="C89" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I89">
+            <v>3</v>
+          </cell>
+          <cell r="M89">
+            <v>854000</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="C90" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I90">
+            <v>1</v>
+          </cell>
+          <cell r="M90">
+            <v>4000000</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="C91" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I91">
+            <v>0</v>
+          </cell>
+          <cell r="M91">
+            <v>2900000</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I92">
+            <v>3</v>
+          </cell>
+          <cell r="M92">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I93">
+            <v>0</v>
+          </cell>
+          <cell r="M93">
+            <v>660000</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="C94" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I94">
+            <v>0</v>
+          </cell>
+          <cell r="M94">
+            <v>592000</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="C95" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I95">
+            <v>3</v>
+          </cell>
+          <cell r="M95">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="C96" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I96">
+            <v>0</v>
+          </cell>
+          <cell r="M96">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="C97" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I97">
+            <v>0</v>
+          </cell>
+          <cell r="M97">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="C98" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I98">
+            <v>0</v>
+          </cell>
+          <cell r="M98">
+            <v>217000</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="C99" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I99">
+            <v>3</v>
+          </cell>
+          <cell r="M99">
+            <v>522000</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="C100" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I100">
+            <v>3</v>
+          </cell>
+          <cell r="M100">
+            <v>175000</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="C101" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I101">
+            <v>0</v>
+          </cell>
+          <cell r="M101">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="C102" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I102">
+            <v>0</v>
+          </cell>
+          <cell r="M102">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="C103" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I103">
+            <v>0</v>
+          </cell>
+          <cell r="M103">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="C104" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I104">
+            <v>0</v>
+          </cell>
+          <cell r="M104">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="C105" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I105">
+            <v>0</v>
+          </cell>
+          <cell r="M105">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="C106" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I106">
+            <v>0</v>
+          </cell>
+          <cell r="M106">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="C107" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I107">
+            <v>0</v>
+          </cell>
+          <cell r="M107">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="C108" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I108">
+            <v>0</v>
+          </cell>
+          <cell r="M108">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="C109" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I109">
+            <v>0</v>
+          </cell>
+          <cell r="M109">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="C110" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I110">
+            <v>0</v>
+          </cell>
+          <cell r="M110">
+            <v>285000</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="C111" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I111">
+            <v>4</v>
+          </cell>
+          <cell r="M111">
+            <v>325200</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="C112" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I112">
+            <v>0</v>
+          </cell>
+          <cell r="M112">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="C113" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I113">
+            <v>0</v>
+          </cell>
+          <cell r="M113">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="C114" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I114">
+            <v>0</v>
+          </cell>
+          <cell r="M114">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="C115" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I115">
+            <v>2</v>
+          </cell>
+          <cell r="M115">
+            <v>277000</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="C116" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I116">
+            <v>0</v>
+          </cell>
+          <cell r="M116">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="C117" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I117">
+            <v>0</v>
+          </cell>
+          <cell r="M117">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="C118" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I118">
+            <v>0</v>
+          </cell>
+          <cell r="M118">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="C119" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I119">
+            <v>0</v>
+          </cell>
+          <cell r="M119">
+            <v>3133000</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="C120" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I120">
+            <v>0</v>
+          </cell>
+          <cell r="M120">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="C121" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I121">
+            <v>0</v>
+          </cell>
+          <cell r="M121">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="C122" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I122">
+            <v>0</v>
+          </cell>
+          <cell r="M122">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="C123" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I123">
+            <v>0</v>
+          </cell>
+          <cell r="M123">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="C124" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I124">
+            <v>0</v>
+          </cell>
+          <cell r="M124">
+            <v>566000</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="C125" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I125">
+            <v>0</v>
+          </cell>
+          <cell r="M125">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="C126" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I126">
+            <v>0</v>
+          </cell>
+          <cell r="M126">
+            <v>338000</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="C127" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I127">
+            <v>0</v>
+          </cell>
+          <cell r="M127">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="C128" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I128">
+            <v>5</v>
+          </cell>
+          <cell r="M128">
+            <v>659000</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="C129" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I129">
+            <v>0</v>
+          </cell>
+          <cell r="M129">
+            <v>218400</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="C130" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I130">
+            <v>0</v>
+          </cell>
+          <cell r="M130">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="C131" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I131">
+            <v>0</v>
+          </cell>
+          <cell r="M131">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="C132" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I132">
+            <v>0</v>
+          </cell>
+          <cell r="M132">
+            <v>1500000</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="C133" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I133">
+            <v>0</v>
+          </cell>
+          <cell r="M133">
+            <v>116400</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="C134" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I134">
+            <v>0</v>
+          </cell>
+          <cell r="M134">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="C135" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I135">
+            <v>0</v>
+          </cell>
+          <cell r="M135">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="C136" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I136">
+            <v>0</v>
+          </cell>
+          <cell r="M136">
+            <v>3151000</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="C137" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I137">
+            <v>0</v>
+          </cell>
+          <cell r="M137">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="C138" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I138">
+            <v>0</v>
+          </cell>
+          <cell r="M138">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="C139" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I139">
+            <v>0</v>
+          </cell>
+          <cell r="M139">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="C140" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I140">
+            <v>0</v>
+          </cell>
+          <cell r="M140">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="C141" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I141">
+            <v>0</v>
+          </cell>
+          <cell r="M141">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="C142" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I142">
+            <v>3</v>
+          </cell>
+          <cell r="M142">
+            <v>325200</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="C143" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I143">
+            <v>0</v>
+          </cell>
+          <cell r="M143">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="C144" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I144">
+            <v>0</v>
+          </cell>
+          <cell r="M144">
+            <v>3320000</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="C145" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I145">
+            <v>0</v>
+          </cell>
+          <cell r="M145">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="C146" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I146">
+            <v>0</v>
+          </cell>
+          <cell r="M146">
+            <v>1320000</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="C147" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I147">
+            <v>0</v>
+          </cell>
+          <cell r="M147">
+            <v>324900</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="C148" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I148">
+            <v>0</v>
+          </cell>
+          <cell r="M148">
+            <v>425000</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="C149" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I149">
+            <v>0</v>
+          </cell>
+          <cell r="M149">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="C150" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I150">
+            <v>0</v>
+          </cell>
+          <cell r="M150">
+            <v>2795000</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="C151" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I151">
+            <v>6</v>
+          </cell>
+          <cell r="M151">
+            <v>1339900</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="C152" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I152">
+            <v>0</v>
+          </cell>
+          <cell r="M152">
+            <v>217000</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="C153" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I153">
+            <v>0</v>
+          </cell>
+          <cell r="M153">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="C154" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I154">
+            <v>0</v>
+          </cell>
+          <cell r="M154">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="C155" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I155">
+            <v>3</v>
+          </cell>
+          <cell r="M155">
+            <v>375200</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="C156" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I156">
+            <v>0</v>
+          </cell>
+          <cell r="M156">
+            <v>702000</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="C157" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I157">
+            <v>0</v>
+          </cell>
+          <cell r="M157">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="C158" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I158">
+            <v>0</v>
+          </cell>
+          <cell r="M158">
+            <v>247000</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="C159" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I159">
+            <v>0</v>
+          </cell>
+          <cell r="M159">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="C160" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I160">
+            <v>3</v>
+          </cell>
+          <cell r="M160">
+            <v>90000</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="C161" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I161">
+            <v>0</v>
+          </cell>
+          <cell r="M161">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="C162" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I162">
+            <v>0</v>
+          </cell>
+          <cell r="M162">
+            <v>5000000</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="C163" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I163">
+            <v>0</v>
+          </cell>
+          <cell r="M163">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="C164" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I164">
+            <v>0</v>
+          </cell>
+          <cell r="M164">
+            <v>379000</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="C165" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I165">
+            <v>0</v>
+          </cell>
+          <cell r="M165">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="C166" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I166">
+            <v>0</v>
+          </cell>
+          <cell r="M166">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="C167" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I167">
+            <v>0</v>
+          </cell>
+          <cell r="M167">
+            <v>2170000</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="C168" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I168">
+            <v>0</v>
+          </cell>
+          <cell r="M168">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="C169" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I169">
+            <v>0</v>
+          </cell>
+          <cell r="M169">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="C170" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I170">
+            <v>0</v>
+          </cell>
+          <cell r="M170">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="C171" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I171">
+            <v>3</v>
+          </cell>
+          <cell r="M171">
+            <v>285500</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="C172" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I172">
+            <v>0</v>
+          </cell>
+          <cell r="M172">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="C173" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I173">
+            <v>0</v>
+          </cell>
+          <cell r="M173">
+            <v>3020000</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="C174" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I174">
+            <v>0</v>
+          </cell>
+          <cell r="M174">
+            <v>117600</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="C175" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I175">
+            <v>3</v>
+          </cell>
+          <cell r="M175">
+            <v>238800</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="C176" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I176">
+            <v>0</v>
+          </cell>
+          <cell r="M176">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="C177" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I177">
+            <v>0</v>
+          </cell>
+          <cell r="M177">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="C178" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I178">
+            <v>0</v>
+          </cell>
+          <cell r="M178">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="C179" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I179">
+            <v>0</v>
+          </cell>
+          <cell r="M179">
+            <v>425000</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="C180" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I180">
+            <v>0</v>
+          </cell>
+          <cell r="M180">
+            <v>258500</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="C181" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I181">
+            <v>0</v>
+          </cell>
+          <cell r="M181">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="C182" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I182">
+            <v>0</v>
+          </cell>
+          <cell r="M182">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="C183" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I183">
+            <v>0</v>
+          </cell>
+          <cell r="M183">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="C184" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I184">
+            <v>0</v>
+          </cell>
+          <cell r="M184">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="C185" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I185">
+            <v>0</v>
+          </cell>
+          <cell r="M185">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="C186" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I186">
+            <v>0</v>
+          </cell>
+          <cell r="M186">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="C187" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I187">
+            <v>0</v>
+          </cell>
+          <cell r="M187">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="C188" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I188">
+            <v>0</v>
+          </cell>
+          <cell r="M188">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="C189" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I189">
+            <v>0</v>
+          </cell>
+          <cell r="M189">
+            <v>145000</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="C190" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I190">
+            <v>0</v>
+          </cell>
+          <cell r="M190">
+            <v>3133000</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="C191" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I191">
+            <v>0</v>
+          </cell>
+          <cell r="M191">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="C192" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I192">
+            <v>0</v>
+          </cell>
+          <cell r="M192">
+            <v>100000</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="C193" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I193">
+            <v>2</v>
+          </cell>
+          <cell r="M193">
+            <v>2000000</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="C194" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I194">
+            <v>0</v>
+          </cell>
+          <cell r="M194">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="C195" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I195">
+            <v>0</v>
+          </cell>
+          <cell r="M195">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="C196" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I196">
+            <v>3</v>
+          </cell>
+          <cell r="M196">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="C197" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I197">
+            <v>0</v>
+          </cell>
+          <cell r="M197">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="C198" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I198">
+            <v>0</v>
+          </cell>
+          <cell r="M198">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="C199" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I199">
+            <v>0</v>
+          </cell>
+          <cell r="M199">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="C200" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I200">
+            <v>0</v>
+          </cell>
+          <cell r="M200">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="C201" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I201">
+            <v>0</v>
+          </cell>
+          <cell r="M201">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="C202" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I202">
+            <v>0</v>
+          </cell>
+          <cell r="M202">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="C203" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I203">
+            <v>0</v>
+          </cell>
+          <cell r="M203">
+            <v>1168000</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="C204" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I204">
+            <v>0</v>
+          </cell>
+          <cell r="M204">
+            <v>1000000</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="C205" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I205">
+            <v>0</v>
+          </cell>
+          <cell r="M205">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="C206" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I206">
+            <v>0</v>
+          </cell>
+          <cell r="M206">
+            <v>145000</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="C207" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I207">
+            <v>0</v>
+          </cell>
+          <cell r="M207">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="C208" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I208">
+            <v>0</v>
+          </cell>
+          <cell r="M208">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="C209" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I209">
+            <v>0</v>
+          </cell>
+          <cell r="M209">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="C210" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I210">
+            <v>0</v>
+          </cell>
+          <cell r="M210">
+            <v>234000</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="C211" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I211">
+            <v>0</v>
+          </cell>
+          <cell r="M211">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="C212" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I212">
+            <v>0</v>
+          </cell>
+          <cell r="M212">
+            <v>2935000</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="C213" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I213">
+            <v>0</v>
+          </cell>
+          <cell r="M213">
+            <v>500000</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="C214" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I214">
+            <v>0</v>
+          </cell>
+          <cell r="M214">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="C215" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I215">
+            <v>0</v>
+          </cell>
+          <cell r="M215">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="C216" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I216">
+            <v>0</v>
+          </cell>
+          <cell r="M216">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="C217" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I217">
+            <v>0</v>
+          </cell>
+          <cell r="M217">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="C218" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I218">
+            <v>0</v>
+          </cell>
+          <cell r="M218">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="C219" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I219">
+            <v>0</v>
+          </cell>
+          <cell r="M219">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="C220" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I220">
+            <v>0</v>
+          </cell>
+          <cell r="M220">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="C221" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I221">
+            <v>0</v>
+          </cell>
+          <cell r="M221">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="C222" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I222">
+            <v>0</v>
+          </cell>
+          <cell r="M222">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="C223" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I223">
+            <v>0</v>
+          </cell>
+          <cell r="M223">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="C224" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I224">
+            <v>0</v>
+          </cell>
+          <cell r="M224">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="C225" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I225">
+            <v>0</v>
+          </cell>
+          <cell r="M225">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="C226" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I226">
+            <v>0</v>
+          </cell>
+          <cell r="M226">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="C227" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I227">
+            <v>0</v>
+          </cell>
+          <cell r="M227">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="C228" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I228">
+            <v>0</v>
+          </cell>
+          <cell r="M228">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="C229" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I229">
+            <v>0</v>
+          </cell>
+          <cell r="M229">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="C230" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I230">
+            <v>0</v>
+          </cell>
+          <cell r="M230">
+            <v>3020000</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="C231" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I231">
+            <v>0</v>
+          </cell>
+          <cell r="M231">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="C232" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I232">
+            <v>0</v>
+          </cell>
+          <cell r="M232">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="C233" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I233">
+            <v>0</v>
+          </cell>
+          <cell r="M233">
+            <v>385000</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="C234" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I234">
+            <v>0</v>
+          </cell>
+          <cell r="M234">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="C235" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I235">
+            <v>0</v>
+          </cell>
+          <cell r="M235">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="C236" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I236">
+            <v>0</v>
+          </cell>
+          <cell r="M236">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="C237" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I237">
+            <v>3</v>
+          </cell>
+          <cell r="M237">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="C238" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I238">
+            <v>0</v>
+          </cell>
+          <cell r="M238">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="C239" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I239">
+            <v>0</v>
+          </cell>
+          <cell r="M239">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="C240" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I240">
+            <v>0</v>
+          </cell>
+          <cell r="M240">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="C241" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I241">
+            <v>0</v>
+          </cell>
+          <cell r="M241">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="C242" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I242">
+            <v>0</v>
+          </cell>
+          <cell r="M242">
+            <v>2795000</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="C243" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I243">
+            <v>0</v>
+          </cell>
+          <cell r="M243">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="C244" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I244">
+            <v>0</v>
+          </cell>
+          <cell r="M244">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="C245" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I245">
+            <v>0</v>
+          </cell>
+          <cell r="M245">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="C246" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I246">
+            <v>3</v>
+          </cell>
+          <cell r="M246">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="C247" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I247">
+            <v>0</v>
+          </cell>
+          <cell r="M247">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="C248" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I248">
+            <v>0</v>
+          </cell>
+          <cell r="M248">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="C249" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I249">
+            <v>0</v>
+          </cell>
+          <cell r="M249">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="C250" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I250">
+            <v>0</v>
+          </cell>
+          <cell r="M250">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="C251" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I251">
+            <v>0</v>
+          </cell>
+          <cell r="M251">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="C252" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I252">
+            <v>0</v>
+          </cell>
+          <cell r="M252">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="C253" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I253">
+            <v>0</v>
+          </cell>
+          <cell r="M253">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="C254" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I254">
+            <v>0</v>
+          </cell>
+          <cell r="M254">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="C255" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I255">
+            <v>0</v>
+          </cell>
+          <cell r="M255">
+            <v>5813000</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="C256" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I256">
+            <v>0</v>
+          </cell>
+          <cell r="M256">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="C257" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I257">
+            <v>0</v>
+          </cell>
+          <cell r="M257">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="C258" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I258">
+            <v>0</v>
+          </cell>
+          <cell r="M258">
+            <v>220800</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="C259" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I259">
+            <v>0</v>
+          </cell>
+          <cell r="M259">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="C260" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I260">
+            <v>0</v>
+          </cell>
+          <cell r="M260">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="C261" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I261">
+            <v>0</v>
+          </cell>
+          <cell r="M261">
+            <v>168000</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="C262" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I262">
+            <v>0</v>
+          </cell>
+          <cell r="M262">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="C263" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I263">
+            <v>3</v>
+          </cell>
+          <cell r="M263">
+            <v>3090000</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="C264" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I264">
+            <v>0</v>
+          </cell>
+          <cell r="M264">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="C265" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I265">
+            <v>0</v>
+          </cell>
+          <cell r="M265">
+            <v>336000</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="C266" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I266">
+            <v>0</v>
+          </cell>
+          <cell r="M266">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="C267" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I267">
+            <v>0</v>
+          </cell>
+          <cell r="M267">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="C268" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I268">
+            <v>0</v>
+          </cell>
+          <cell r="M268">
+            <v>3681000</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="C269" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I269">
+            <v>0</v>
+          </cell>
+          <cell r="M269">
+            <v>2900000</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="C270" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I270">
+            <v>0</v>
+          </cell>
+          <cell r="M270">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="C271" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I271">
+            <v>0</v>
+          </cell>
+          <cell r="M271">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="C272" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I272">
+            <v>0</v>
+          </cell>
+          <cell r="M272">
+            <v>2650000</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="C273" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I273">
+            <v>0</v>
+          </cell>
+          <cell r="M273">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="C274" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I274">
+            <v>0</v>
+          </cell>
+          <cell r="M274">
+            <v>3740000</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="C275" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I275">
+            <v>0</v>
+          </cell>
+          <cell r="M275">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="C276" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I276">
+            <v>0</v>
+          </cell>
+          <cell r="M276">
+            <v>2495000</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="C277" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I277">
+            <v>0</v>
+          </cell>
+          <cell r="M277">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="C278" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I278">
+            <v>0</v>
+          </cell>
+          <cell r="M278">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="C279" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I279">
+            <v>0</v>
+          </cell>
+          <cell r="M279">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="C280" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I280">
+            <v>6</v>
+          </cell>
+          <cell r="M280">
+            <v>630000</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="C281" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I281">
+            <v>0</v>
+          </cell>
+          <cell r="M281">
+            <v>3740000</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="C282" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I282">
+            <v>0</v>
+          </cell>
+          <cell r="M282">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="C283" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I283">
+            <v>0</v>
+          </cell>
+          <cell r="M283">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="C284" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I284">
+            <v>0</v>
+          </cell>
+          <cell r="M284">
+            <v>600000</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="C285" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I285">
+            <v>0</v>
+          </cell>
+          <cell r="M285">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="C286" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I286">
+            <v>0</v>
+          </cell>
+          <cell r="M286">
+            <v>170000</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="C287" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I287">
+            <v>0</v>
+          </cell>
+          <cell r="M287">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="C288" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I288">
+            <v>0</v>
+          </cell>
+          <cell r="M288">
+            <v>145000</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="C289" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I289">
+            <v>0</v>
+          </cell>
+          <cell r="M289">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="C290" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I290">
+            <v>0</v>
+          </cell>
+          <cell r="M290">
+            <v>2650000</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="C291" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I291">
+            <v>0</v>
+          </cell>
+          <cell r="M291">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="C292" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I292">
+            <v>0</v>
+          </cell>
+          <cell r="M292">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="C293" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I293">
+            <v>0</v>
+          </cell>
+          <cell r="M293">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="C294" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I294">
+            <v>0</v>
+          </cell>
+          <cell r="M294">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="C295" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I295">
+            <v>0</v>
+          </cell>
+          <cell r="M295">
+            <v>3190000</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="C296" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I296">
+            <v>0</v>
+          </cell>
+          <cell r="M296">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="C297" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I297">
+            <v>0</v>
+          </cell>
+          <cell r="M297">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="C298" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I298">
+            <v>0</v>
+          </cell>
+          <cell r="M298">
+            <v>2350000</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="C299" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I299">
+            <v>0</v>
+          </cell>
+          <cell r="M299">
+            <v>840000</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="C300" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I300">
+            <v>0</v>
+          </cell>
+          <cell r="M300">
+            <v>132000</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="C301" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I301">
+            <v>0</v>
+          </cell>
+          <cell r="M301">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="C302" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I302">
+            <v>0</v>
+          </cell>
+          <cell r="M302">
+            <v>1072000</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="C303" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I303">
+            <v>3</v>
+          </cell>
+          <cell r="M303">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="C304" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I304">
+            <v>3</v>
+          </cell>
+          <cell r="M304">
+            <v>308400</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="C305" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I305">
+            <v>0</v>
+          </cell>
+          <cell r="M305">
+            <v>85000</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="C306" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I306">
+            <v>0</v>
+          </cell>
+          <cell r="M306">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="C307" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I307">
+            <v>0</v>
+          </cell>
+          <cell r="M307">
+            <v>302400</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="C308" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I308">
+            <v>4</v>
+          </cell>
+          <cell r="M308">
+            <v>522000</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="C309" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I309">
+            <v>0</v>
+          </cell>
+          <cell r="M309">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="C310" t="str">
+            <v>DSE-JAGOIBABNG01</v>
+          </cell>
+          <cell r="I310">
+            <v>0</v>
+          </cell>
+          <cell r="M310">
+            <v>324900</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="C311" t="str">
+            <v>DSE-BENGKAYANG01</v>
+          </cell>
+          <cell r="I311">
+            <v>0</v>
+          </cell>
+          <cell r="M311">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="C312" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I312">
+            <v>0</v>
+          </cell>
+          <cell r="M312">
+            <v>660000</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="C313" t="str">
+            <v>DSE-JAGOIBABNG02</v>
+          </cell>
+          <cell r="I313">
+            <v>0</v>
+          </cell>
+          <cell r="M313">
+            <v>1670000</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="C314" t="str">
+            <v>DSE1147</v>
+          </cell>
+          <cell r="I314">
+            <v>4</v>
+          </cell>
+          <cell r="M314">
+            <v>590000</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="C315" t="str">
+            <v>DSE1082</v>
+          </cell>
+          <cell r="I315">
+            <v>0</v>
+          </cell>
+          <cell r="M315">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -843,19 +4283,20 @@
         <v>621760720.32094395</v>
       </c>
       <c r="D4" s="20">
-        <v>287678000</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
+        <v>80905000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.46268281446197623</v>
+        <v>0.13012240457750049</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-334082720.32094395</v>
+        <v>-540855720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18560151.128941331</v>
+        <v>-30047540.017830219</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -869,19 +4310,20 @@
         <v>575117071.19165206</v>
       </c>
       <c r="D5" s="20">
-        <v>268398600</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
+        <v>44462000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.46668515584813658</v>
+        <v>7.7309477021563627E-2</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-306718471.19165206</v>
+        <v>-530655071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-17039915.066202894</v>
+        <v>-29480837.288425114</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -895,19 +4337,20 @@
         <v>91900861.058193401</v>
       </c>
       <c r="D6" s="20">
-        <v>44100000</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
+        <v>21171500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.479864927185775</v>
+        <v>0.23037324956720262</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-47800861.058193401</v>
+        <v>-70729361.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-2655603.3921218556</v>
+        <v>-3929408.9476774111</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -921,19 +4364,20 @@
         <v>241784636.953421</v>
       </c>
       <c r="D7" s="20">
-        <v>200803400</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
+        <v>14152400</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.83050520715542442</v>
+        <v>5.8533082078024719E-2</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-40981236.953420997</v>
+        <v>-227632236.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-2276735.3863011664</v>
+        <v>-12646235.386301167</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -947,19 +4391,20 @@
         <v>451939961.27051902</v>
       </c>
       <c r="D8" s="20">
-        <v>185786050</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
+        <v>29902900</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.41108568819120977</v>
+        <v>6.6165647126966348E-2</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-266153911.27051902</v>
+        <v>-422037061.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-14786328.403917722</v>
+        <v>-23446503.403917722</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -999,19 +4444,20 @@
         <v>744.32125870725895</v>
       </c>
       <c r="D11" s="10">
-        <v>1118</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
+        <v>12</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>1.5020395923418179</v>
+        <v>1.6122070758588385E-2</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>373.67874129274105</v>
+        <v>-732.32125870725895</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>20.759930071818946</v>
+        <v>-40.6845143726255</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -1025,19 +4471,20 @@
         <v>397.981099231874</v>
       </c>
       <c r="D12" s="10">
-        <v>612</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
+        <v>38</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.5377614695300721</v>
+        <v>9.5481921310690748E-2</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>214.018900768126</v>
+        <v>-359.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>11.889938931562556</v>
+        <v>-19.998949957326332</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -1051,6 +4498,7 @@
         <v>75</v>
       </c>
       <c r="D13" s="10">
+        <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
         <v>0</v>
       </c>
       <c r="E13" s="9">
@@ -1077,19 +4525,20 @@
         <v>324.753531078332</v>
       </c>
       <c r="D14" s="10">
-        <v>402</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
+        <v>34</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>1.2378618291390828</v>
+        <v>0.10469478156897714</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>77.246468921667997</v>
+        <v>-290.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>4.2914704956482224</v>
+        <v>-16.152973948796223</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -1103,19 +4552,20 @@
         <v>398.57741493344997</v>
       </c>
       <c r="D15" s="10">
-        <v>448</v>
+        <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
+        <v>30</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.1239974549857574</v>
+        <v>7.5267686717796253E-2</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>49.422585066550027</v>
+        <v>-368.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>2.7456991703638902</v>
+        <v>-20.476523051858333</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -921,7 +921,7 @@
             <v>0</v>
           </cell>
           <cell r="M39">
-            <v>461500</v>
+            <v>761500</v>
           </cell>
         </row>
         <row r="40">
@@ -1251,7 +1251,7 @@
             <v>0</v>
           </cell>
           <cell r="M69">
-            <v>800000</v>
+            <v>1100000</v>
           </cell>
         </row>
         <row r="70">
@@ -1702,7 +1702,7 @@
             <v>0</v>
           </cell>
           <cell r="M110">
-            <v>285000</v>
+            <v>3255000</v>
           </cell>
         </row>
         <row r="111">
@@ -1710,7 +1710,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I111">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="M111">
             <v>325200</v>
@@ -2326,7 +2326,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I167">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M167">
             <v>2170000</v>
@@ -2395,7 +2395,7 @@
             <v>0</v>
           </cell>
           <cell r="M173">
-            <v>3020000</v>
+            <v>5990000</v>
           </cell>
         </row>
         <row r="174">
@@ -2824,7 +2824,7 @@
             <v>0</v>
           </cell>
           <cell r="M212">
-            <v>2935000</v>
+            <v>5905000</v>
           </cell>
         </row>
         <row r="213">
@@ -3022,7 +3022,7 @@
             <v>0</v>
           </cell>
           <cell r="M230">
-            <v>3020000</v>
+            <v>6520000</v>
           </cell>
         </row>
         <row r="231">
@@ -3946,7 +3946,7 @@
             <v>4</v>
           </cell>
           <cell r="M314">
-            <v>590000</v>
+            <v>1040000</v>
           </cell>
         </row>
         <row r="315">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>44462000</v>
+        <v>57322000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>7.7309477021563627E-2</v>
+        <v>9.9670141735191189E-2</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-530655071.19165206</v>
+        <v>-517795071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-29480837.288425114</v>
+        <v>-28766392.84398067</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>29902900</v>
+        <v>30502900</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>6.6165647126966348E-2</v>
+        <v>6.7493257100453202E-2</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-422037061.27051902</v>
+        <v>-421437061.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-23446503.403917722</v>
+        <v>-23413170.07058439</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.10469478156897714</v>
+        <v>0.10777403985041765</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-290.753531078332</v>
+        <v>-289.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-16.152973948796223</v>
+        <v>-16.097418393240666</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>7.5267686717796253E-2</v>
+        <v>7.777660960838946E-2</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-368.57741493344997</v>
+        <v>-367.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-20.476523051858333</v>
+        <v>-20.420967496302776</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -552,24 +552,24 @@
         </row>
         <row r="6">
           <cell r="C6" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I6">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M6">
-            <v>260000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I7">
             <v>0</v>
           </cell>
           <cell r="M7">
-            <v>3190000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="8">
@@ -580,45 +580,45 @@
             <v>0</v>
           </cell>
           <cell r="M8">
-            <v>233000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I9">
             <v>0</v>
           </cell>
           <cell r="M9">
-            <v>302400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I10">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M10">
-            <v>1090000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I11">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M11">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I12">
             <v>0</v>
@@ -629,68 +629,68 @@
         </row>
         <row r="13">
           <cell r="C13" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I13">
             <v>0</v>
           </cell>
           <cell r="M13">
-            <v>85000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I14">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M14">
-            <v>660000</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I15">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M15">
-            <v>660000</v>
+            <v>590000</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I16">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="M16">
-            <v>3134000</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I17">
             <v>0</v>
           </cell>
           <cell r="M17">
-            <v>132000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I18">
             <v>0</v>
           </cell>
           <cell r="M18">
-            <v>2350000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="19">
@@ -698,48 +698,48 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I19">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M19">
-            <v>3322000</v>
+            <v>590000</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I20">
             <v>0</v>
           </cell>
           <cell r="M20">
-            <v>302400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I21">
             <v>0</v>
           </cell>
           <cell r="M21">
-            <v>302400</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I22">
             <v>0</v>
           </cell>
           <cell r="M22">
-            <v>0</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I23">
             <v>0</v>
@@ -761,68 +761,68 @@
         </row>
         <row r="25">
           <cell r="C25" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I25">
             <v>0</v>
           </cell>
           <cell r="M25">
-            <v>302400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I26">
             <v>0</v>
           </cell>
           <cell r="M26">
-            <v>300000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I27">
             <v>0</v>
           </cell>
           <cell r="M27">
-            <v>3526000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I28">
             <v>0</v>
           </cell>
           <cell r="M28">
-            <v>318000</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I29">
             <v>0</v>
           </cell>
           <cell r="M29">
-            <v>85000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I30">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M30">
-            <v>470000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="31">
@@ -838,24 +838,24 @@
         </row>
         <row r="32">
           <cell r="C32" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I32">
             <v>0</v>
           </cell>
           <cell r="M32">
-            <v>85000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I33">
             <v>0</v>
           </cell>
           <cell r="M33">
-            <v>650000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="34">
@@ -871,13 +871,13 @@
         </row>
         <row r="35">
           <cell r="C35" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I35">
             <v>0</v>
           </cell>
           <cell r="M35">
-            <v>132000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="36">
@@ -885,21 +885,21 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I36">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M36">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I37">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M37">
-            <v>302400</v>
+            <v>133500</v>
           </cell>
         </row>
         <row r="38">
@@ -907,65 +907,65 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I38">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M38">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I39">
             <v>0</v>
           </cell>
           <cell r="M39">
-            <v>761500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I40">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M40">
-            <v>200000</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I41">
             <v>0</v>
           </cell>
           <cell r="M41">
-            <v>500000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I42">
             <v>0</v>
           </cell>
           <cell r="M42">
-            <v>324900</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I43">
             <v>0</v>
           </cell>
           <cell r="M43">
-            <v>747000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="44">
@@ -973,21 +973,21 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I44">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M44">
-            <v>425000</v>
+            <v>3616000</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I45">
             <v>3</v>
           </cell>
           <cell r="M45">
-            <v>558000</v>
+            <v>3326000</v>
           </cell>
         </row>
         <row r="46">
@@ -995,109 +995,109 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I46">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M46">
-            <v>3200000</v>
+            <v>3326000</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I47">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M47">
-            <v>1000000</v>
+            <v>277000</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I48">
             <v>0</v>
           </cell>
           <cell r="M48">
-            <v>0</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I49">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M49">
-            <v>3189200</v>
+            <v>145000</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I50">
             <v>0</v>
           </cell>
           <cell r="M50">
-            <v>1000000</v>
+            <v>3200000</v>
           </cell>
         </row>
         <row r="51">
           <cell r="C51" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I51">
             <v>0</v>
           </cell>
           <cell r="M51">
-            <v>302400</v>
+            <v>2650000</v>
           </cell>
         </row>
         <row r="52">
           <cell r="C52" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I52">
             <v>0</v>
           </cell>
           <cell r="M52">
-            <v>0</v>
+            <v>2495000</v>
           </cell>
         </row>
         <row r="53">
           <cell r="C53" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I53">
             <v>0</v>
           </cell>
           <cell r="M53">
-            <v>0</v>
+            <v>2650000</v>
           </cell>
         </row>
         <row r="54">
           <cell r="C54" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I54">
             <v>0</v>
           </cell>
           <cell r="M54">
-            <v>500000</v>
+            <v>3380000</v>
           </cell>
         </row>
         <row r="55">
           <cell r="C55" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I55">
             <v>0</v>
           </cell>
           <cell r="M55">
-            <v>432000</v>
+            <v>3222000</v>
           </cell>
         </row>
         <row r="56">
@@ -1105,21 +1105,21 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I56">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M56">
-            <v>840000</v>
+            <v>426000</v>
           </cell>
         </row>
         <row r="57">
           <cell r="C57" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I57">
             <v>0</v>
           </cell>
           <cell r="M57">
-            <v>132000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="58">
@@ -1130,7 +1130,7 @@
             <v>0</v>
           </cell>
           <cell r="M58">
-            <v>3190000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="59">
@@ -1141,117 +1141,117 @@
             <v>0</v>
           </cell>
           <cell r="M59">
-            <v>840000</v>
+            <v>145000</v>
           </cell>
         </row>
         <row r="60">
           <cell r="C60" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I60">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M60">
-            <v>692000</v>
+            <v>660000</v>
           </cell>
         </row>
         <row r="61">
           <cell r="C61" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I61">
             <v>0</v>
           </cell>
           <cell r="M61">
-            <v>85000</v>
+            <v>660000</v>
           </cell>
         </row>
         <row r="62">
           <cell r="C62" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I62">
             <v>0</v>
           </cell>
           <cell r="M62">
-            <v>352800</v>
+            <v>3526000</v>
           </cell>
         </row>
         <row r="63">
           <cell r="C63" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I63">
             <v>0</v>
           </cell>
           <cell r="M63">
-            <v>0</v>
+            <v>3190000</v>
           </cell>
         </row>
         <row r="64">
           <cell r="C64" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I64">
             <v>0</v>
           </cell>
           <cell r="M64">
-            <v>0</v>
+            <v>660000</v>
           </cell>
         </row>
         <row r="65">
           <cell r="C65" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I65">
             <v>0</v>
           </cell>
           <cell r="M65">
-            <v>234000</v>
+            <v>5000000</v>
           </cell>
         </row>
         <row r="66">
           <cell r="C66" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I66">
             <v>0</v>
           </cell>
           <cell r="M66">
-            <v>2875000</v>
+            <v>2795000</v>
           </cell>
         </row>
         <row r="67">
           <cell r="C67" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I67">
             <v>0</v>
           </cell>
           <cell r="M67">
-            <v>302400</v>
+            <v>660000</v>
           </cell>
         </row>
         <row r="68">
           <cell r="C68" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I68">
             <v>0</v>
           </cell>
           <cell r="M68">
-            <v>500000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="69">
           <cell r="C69" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I69">
             <v>0</v>
           </cell>
           <cell r="M69">
-            <v>1100000</v>
+            <v>425000</v>
           </cell>
         </row>
         <row r="70">
@@ -1278,73 +1278,73 @@
         </row>
         <row r="72">
           <cell r="C72" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I72">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M72">
-            <v>1000000</v>
+            <v>702000</v>
           </cell>
         </row>
         <row r="73">
           <cell r="C73" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I73">
             <v>0</v>
           </cell>
           <cell r="M73">
-            <v>0</v>
+            <v>425000</v>
           </cell>
         </row>
         <row r="74">
           <cell r="C74" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I74">
             <v>0</v>
           </cell>
           <cell r="M74">
-            <v>313000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="75">
           <cell r="C75" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I75">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M75">
-            <v>168000</v>
+            <v>1072000</v>
           </cell>
         </row>
         <row r="76">
           <cell r="C76" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I76">
             <v>0</v>
           </cell>
           <cell r="M76">
-            <v>324900</v>
+            <v>747000</v>
           </cell>
         </row>
         <row r="77">
           <cell r="C77" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I77">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M77">
-            <v>422000</v>
+            <v>592000</v>
           </cell>
         </row>
         <row r="78">
           <cell r="C78" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I78">
             <v>0</v>
@@ -1355,24 +1355,24 @@
         </row>
         <row r="79">
           <cell r="C79" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I79">
             <v>0</v>
           </cell>
           <cell r="M79">
-            <v>2695000</v>
+            <v>168000</v>
           </cell>
         </row>
         <row r="80">
           <cell r="C80" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I80">
             <v>0</v>
           </cell>
           <cell r="M80">
-            <v>234000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="81">
@@ -1388,13 +1388,13 @@
         </row>
         <row r="82">
           <cell r="C82" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I82">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M82">
-            <v>90000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="83">
@@ -1402,10 +1402,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I83">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M83">
-            <v>325200</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,40 +1416,40 @@
             <v>0</v>
           </cell>
           <cell r="M84">
-            <v>832800</v>
+            <v>405600</v>
           </cell>
         </row>
         <row r="85">
           <cell r="C85" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I85">
             <v>0</v>
           </cell>
           <cell r="M85">
-            <v>0</v>
+            <v>105600</v>
           </cell>
         </row>
         <row r="86">
           <cell r="C86" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I86">
             <v>0</v>
           </cell>
           <cell r="M86">
-            <v>3164000</v>
+            <v>1700800</v>
           </cell>
         </row>
         <row r="87">
           <cell r="C87" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I87">
             <v>0</v>
           </cell>
           <cell r="M87">
-            <v>0</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="88">
@@ -1460,40 +1460,40 @@
             <v>0</v>
           </cell>
           <cell r="M88">
-            <v>838000</v>
+            <v>117000</v>
           </cell>
         </row>
         <row r="89">
           <cell r="C89" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I89">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M89">
-            <v>854000</v>
+            <v>617000</v>
           </cell>
         </row>
         <row r="90">
           <cell r="C90" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I90">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M90">
-            <v>4000000</v>
+            <v>110400</v>
           </cell>
         </row>
         <row r="91">
           <cell r="C91" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I91">
             <v>0</v>
           </cell>
           <cell r="M91">
-            <v>2900000</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="92">
@@ -1501,32 +1501,32 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I92">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M92">
-            <v>308400</v>
+            <v>66000</v>
           </cell>
         </row>
         <row r="93">
           <cell r="C93" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I93">
             <v>0</v>
           </cell>
           <cell r="M93">
-            <v>660000</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="94">
           <cell r="C94" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I94">
             <v>0</v>
           </cell>
           <cell r="M94">
-            <v>592000</v>
+            <v>518000</v>
           </cell>
         </row>
         <row r="95">
@@ -1534,175 +1534,175 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I95">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M95">
-            <v>308400</v>
+            <v>220800</v>
           </cell>
         </row>
         <row r="96">
           <cell r="C96" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I96">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M96">
-            <v>0</v>
+            <v>271200</v>
           </cell>
         </row>
         <row r="97">
           <cell r="C97" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I97">
             <v>0</v>
           </cell>
           <cell r="M97">
-            <v>0</v>
+            <v>273600</v>
           </cell>
         </row>
         <row r="98">
           <cell r="C98" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I98">
             <v>0</v>
           </cell>
           <cell r="M98">
-            <v>217000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="99">
           <cell r="C99" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I99">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M99">
-            <v>522000</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="100">
           <cell r="C100" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I100">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M100">
-            <v>175000</v>
+            <v>1532800</v>
           </cell>
         </row>
         <row r="101">
           <cell r="C101" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I101">
             <v>0</v>
           </cell>
           <cell r="M101">
-            <v>0</v>
+            <v>1552800</v>
           </cell>
         </row>
         <row r="102">
           <cell r="C102" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I102">
             <v>0</v>
           </cell>
           <cell r="M102">
-            <v>0</v>
+            <v>169200</v>
           </cell>
         </row>
         <row r="103">
           <cell r="C103" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I103">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="M103">
-            <v>0</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="104">
           <cell r="C104" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I104">
             <v>0</v>
           </cell>
           <cell r="M104">
-            <v>0</v>
+            <v>2168000</v>
           </cell>
         </row>
         <row r="105">
           <cell r="C105" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I105">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M105">
-            <v>0</v>
+            <v>2285500</v>
           </cell>
         </row>
         <row r="106">
           <cell r="C106" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I106">
             <v>0</v>
           </cell>
           <cell r="M106">
-            <v>0</v>
+            <v>220800</v>
           </cell>
         </row>
         <row r="107">
           <cell r="C107" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I107">
             <v>0</v>
           </cell>
           <cell r="M107">
-            <v>85000</v>
+            <v>170400</v>
           </cell>
         </row>
         <row r="108">
           <cell r="C108" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I108">
             <v>0</v>
           </cell>
           <cell r="M108">
-            <v>0</v>
+            <v>1220800</v>
           </cell>
         </row>
         <row r="109">
           <cell r="C109" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I109">
             <v>0</v>
           </cell>
           <cell r="M109">
-            <v>85000</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="110">
           <cell r="C110" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I110">
             <v>0</v>
           </cell>
           <cell r="M110">
-            <v>3255000</v>
+            <v>220800</v>
           </cell>
         </row>
         <row r="111">
@@ -1710,54 +1710,54 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I111">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="M111">
-            <v>325200</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="112">
           <cell r="C112" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I112">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M112">
-            <v>132000</v>
+            <v>378000</v>
           </cell>
         </row>
         <row r="113">
           <cell r="C113" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I113">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M113">
-            <v>170000</v>
+            <v>578000</v>
           </cell>
         </row>
         <row r="114">
           <cell r="C114" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I114">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M114">
-            <v>0</v>
+            <v>370800</v>
           </cell>
         </row>
         <row r="115">
           <cell r="C115" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I115">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M115">
-            <v>277000</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="116">
@@ -1768,40 +1768,40 @@
             <v>0</v>
           </cell>
           <cell r="M116">
-            <v>0</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="117">
           <cell r="C117" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I117">
             <v>0</v>
           </cell>
           <cell r="M117">
-            <v>300000</v>
+            <v>658400</v>
           </cell>
         </row>
         <row r="118">
           <cell r="C118" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I118">
             <v>0</v>
           </cell>
           <cell r="M118">
-            <v>170000</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="119">
           <cell r="C119" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I119">
             <v>0</v>
           </cell>
           <cell r="M119">
-            <v>3133000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="120">
@@ -1812,62 +1812,62 @@
             <v>0</v>
           </cell>
           <cell r="M120">
-            <v>302400</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="121">
           <cell r="C121" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I121">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M121">
-            <v>0</v>
+            <v>325200</v>
           </cell>
         </row>
         <row r="122">
           <cell r="C122" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I122">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M122">
-            <v>0</v>
+            <v>971500</v>
           </cell>
         </row>
         <row r="123">
           <cell r="C123" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I123">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M123">
-            <v>300000</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="124">
           <cell r="C124" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I124">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M124">
-            <v>566000</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="125">
           <cell r="C125" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I125">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M125">
-            <v>0</v>
+            <v>325200</v>
           </cell>
         </row>
         <row r="126">
@@ -1878,210 +1878,210 @@
             <v>0</v>
           </cell>
           <cell r="M126">
-            <v>338000</v>
+            <v>489200</v>
           </cell>
         </row>
         <row r="127">
           <cell r="C127" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I127">
             <v>0</v>
           </cell>
           <cell r="M127">
-            <v>0</v>
+            <v>3251800</v>
           </cell>
         </row>
         <row r="128">
           <cell r="C128" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I128">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="M128">
-            <v>659000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="129">
           <cell r="C129" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I129">
-            <v>0</v>
+            <v>9</v>
           </cell>
           <cell r="M129">
-            <v>218400</v>
+            <v>1429900</v>
           </cell>
         </row>
         <row r="130">
           <cell r="C130" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I130">
             <v>0</v>
           </cell>
           <cell r="M130">
-            <v>0</v>
+            <v>1052800</v>
           </cell>
         </row>
         <row r="131">
           <cell r="C131" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I131">
             <v>0</v>
           </cell>
           <cell r="M131">
-            <v>0</v>
+            <v>500000</v>
           </cell>
         </row>
         <row r="132">
           <cell r="C132" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M132">
-            <v>1500000</v>
+            <v>2770000</v>
           </cell>
         </row>
         <row r="133">
           <cell r="C133" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I133">
             <v>0</v>
           </cell>
           <cell r="M133">
-            <v>116400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="134">
           <cell r="C134" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I134">
             <v>0</v>
           </cell>
           <cell r="M134">
-            <v>2350000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="135">
           <cell r="C135" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I135">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M135">
-            <v>170000</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="136">
           <cell r="C136" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I136">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M136">
-            <v>3151000</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="137">
           <cell r="C137" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I137">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M137">
-            <v>0</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="138">
           <cell r="C138" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I138">
             <v>0</v>
           </cell>
           <cell r="M138">
-            <v>0</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="139">
           <cell r="C139" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I139">
             <v>0</v>
           </cell>
           <cell r="M139">
-            <v>302400</v>
+            <v>617000</v>
           </cell>
         </row>
         <row r="140">
           <cell r="C140" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I140">
             <v>0</v>
           </cell>
           <cell r="M140">
-            <v>302400</v>
+            <v>417000</v>
           </cell>
         </row>
         <row r="141">
           <cell r="C141" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I141">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M141">
-            <v>170000</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="142">
           <cell r="C142" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I142">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M142">
-            <v>325200</v>
+            <v>168000</v>
           </cell>
         </row>
         <row r="143">
           <cell r="C143" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I143">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M143">
-            <v>0</v>
+            <v>308400</v>
           </cell>
         </row>
         <row r="144">
           <cell r="C144" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I144">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="M144">
-            <v>3320000</v>
+            <v>780000</v>
           </cell>
         </row>
         <row r="145">
           <cell r="C145" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I145">
             <v>0</v>
@@ -2092,13 +2092,13 @@
         </row>
         <row r="146">
           <cell r="C146" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I146">
             <v>0</v>
           </cell>
           <cell r="M146">
-            <v>1320000</v>
+            <v>324900</v>
           </cell>
         </row>
         <row r="147">
@@ -2114,13 +2114,13 @@
         </row>
         <row r="148">
           <cell r="C148" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I148">
             <v>0</v>
           </cell>
           <cell r="M148">
-            <v>425000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="149">
@@ -2142,18 +2142,18 @@
             <v>0</v>
           </cell>
           <cell r="M150">
-            <v>2795000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="151">
           <cell r="C151" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I151">
-            <v>6</v>
+            <v>2</v>
           </cell>
           <cell r="M151">
-            <v>1339900</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="152">
@@ -2161,106 +2161,106 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I152">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M152">
-            <v>217000</v>
+            <v>4000000</v>
           </cell>
         </row>
         <row r="153">
           <cell r="C153" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I153">
             <v>0</v>
           </cell>
           <cell r="M153">
-            <v>840000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="154">
           <cell r="C154" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I154">
             <v>0</v>
           </cell>
           <cell r="M154">
-            <v>840000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="155">
           <cell r="C155" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I155">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M155">
-            <v>375200</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="156">
           <cell r="C156" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I156">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M156">
-            <v>702000</v>
+            <v>234000</v>
           </cell>
         </row>
         <row r="157">
           <cell r="C157" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I157">
             <v>0</v>
           </cell>
           <cell r="M157">
-            <v>0</v>
+            <v>168000</v>
           </cell>
         </row>
         <row r="158">
           <cell r="C158" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I158">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M158">
-            <v>247000</v>
+            <v>234000</v>
           </cell>
         </row>
         <row r="159">
           <cell r="C159" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I159">
             <v>0</v>
           </cell>
           <cell r="M159">
-            <v>0</v>
+            <v>761500</v>
           </cell>
         </row>
         <row r="160">
           <cell r="C160" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I160">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M160">
-            <v>90000</v>
+            <v>1313000</v>
           </cell>
         </row>
         <row r="161">
           <cell r="C161" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I161">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="M161">
             <v>0</v>
@@ -2268,123 +2268,123 @@
         </row>
         <row r="162">
           <cell r="C162" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I162">
             <v>0</v>
           </cell>
           <cell r="M162">
-            <v>5000000</v>
+            <v>5813000</v>
           </cell>
         </row>
         <row r="163">
           <cell r="C163" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I163">
             <v>0</v>
           </cell>
           <cell r="M163">
-            <v>0</v>
+            <v>1670000</v>
           </cell>
         </row>
         <row r="164">
           <cell r="C164" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I164">
             <v>0</v>
           </cell>
           <cell r="M164">
-            <v>379000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="165">
           <cell r="C165" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I165">
             <v>0</v>
           </cell>
           <cell r="M165">
-            <v>840000</v>
+            <v>217000</v>
           </cell>
         </row>
         <row r="166">
           <cell r="C166" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I166">
             <v>0</v>
           </cell>
           <cell r="M166">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="167">
           <cell r="C167" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I167">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M167">
-            <v>2170000</v>
+            <v>2795000</v>
           </cell>
         </row>
         <row r="168">
           <cell r="C168" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I168">
             <v>0</v>
           </cell>
           <cell r="M168">
-            <v>1000000</v>
+            <v>217000</v>
           </cell>
         </row>
         <row r="169">
           <cell r="C169" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I169">
             <v>0</v>
           </cell>
           <cell r="M169">
-            <v>0</v>
+            <v>385000</v>
           </cell>
         </row>
         <row r="170">
           <cell r="C170" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I170">
             <v>0</v>
           </cell>
           <cell r="M170">
-            <v>168000</v>
+            <v>950000</v>
           </cell>
         </row>
         <row r="171">
           <cell r="C171" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I171">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M171">
-            <v>285500</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="172">
           <cell r="C172" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I172">
             <v>0</v>
           </cell>
           <cell r="M172">
-            <v>168000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="173">
@@ -2395,18 +2395,18 @@
             <v>0</v>
           </cell>
           <cell r="M173">
-            <v>5990000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="174">
           <cell r="C174" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I174">
             <v>0</v>
           </cell>
           <cell r="M174">
-            <v>117600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="175">
@@ -2414,10 +2414,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I175">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M175">
-            <v>238800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="176">
@@ -2428,7 +2428,7 @@
             <v>0</v>
           </cell>
           <cell r="M176">
-            <v>168000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="177">
@@ -2444,35 +2444,35 @@
         </row>
         <row r="178">
           <cell r="C178" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I178">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M178">
-            <v>170000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="179">
           <cell r="C179" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I179">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M179">
-            <v>425000</v>
+            <v>692000</v>
           </cell>
         </row>
         <row r="180">
           <cell r="C180" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I180">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="M180">
-            <v>258500</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="181">
@@ -2483,114 +2483,114 @@
             <v>0</v>
           </cell>
           <cell r="M181">
-            <v>85000</v>
+            <v>170000</v>
           </cell>
         </row>
         <row r="182">
           <cell r="C182" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I182">
             <v>0</v>
           </cell>
           <cell r="M182">
-            <v>0</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="183">
           <cell r="C183" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I183">
             <v>0</v>
           </cell>
           <cell r="M183">
-            <v>0</v>
+            <v>432000</v>
           </cell>
         </row>
         <row r="184">
           <cell r="C184" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I184">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M184">
-            <v>0</v>
+            <v>2354000</v>
           </cell>
         </row>
         <row r="185">
           <cell r="C185" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I185">
             <v>0</v>
           </cell>
           <cell r="M185">
-            <v>0</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="186">
           <cell r="C186" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I186">
             <v>0</v>
           </cell>
           <cell r="M186">
-            <v>0</v>
+            <v>170000</v>
           </cell>
         </row>
         <row r="187">
           <cell r="C187" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I187">
             <v>0</v>
           </cell>
           <cell r="M187">
-            <v>0</v>
+            <v>3320000</v>
           </cell>
         </row>
         <row r="188">
           <cell r="C188" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I188">
             <v>0</v>
           </cell>
           <cell r="M188">
-            <v>300000</v>
+            <v>1320000</v>
           </cell>
         </row>
         <row r="189">
           <cell r="C189" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I189">
             <v>0</v>
           </cell>
           <cell r="M189">
-            <v>145000</v>
+            <v>170000</v>
           </cell>
         </row>
         <row r="190">
           <cell r="C190" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I190">
             <v>0</v>
           </cell>
           <cell r="M190">
-            <v>3133000</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="191">
           <cell r="C191" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I191">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M191">
             <v>0</v>
@@ -2598,24 +2598,24 @@
         </row>
         <row r="192">
           <cell r="C192" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I192">
             <v>0</v>
           </cell>
           <cell r="M192">
-            <v>100000</v>
+            <v>1600000</v>
           </cell>
         </row>
         <row r="193">
           <cell r="C193" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I193">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="M193">
-            <v>2000000</v>
+            <v>3007000</v>
           </cell>
         </row>
         <row r="194">
@@ -2626,70 +2626,70 @@
             <v>0</v>
           </cell>
           <cell r="M194">
-            <v>1000000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="195">
           <cell r="C195" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I195">
             <v>0</v>
           </cell>
           <cell r="M195">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="196">
           <cell r="C196" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I196">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M196">
-            <v>308400</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="197">
           <cell r="C197" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I197">
             <v>0</v>
           </cell>
           <cell r="M197">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="198">
           <cell r="C198" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I198">
             <v>0</v>
           </cell>
           <cell r="M198">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="199">
           <cell r="C199" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I199">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M199">
-            <v>1000000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="200">
           <cell r="C200" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I200">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M200">
             <v>0</v>
@@ -2700,120 +2700,120 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I201">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M201">
-            <v>168000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="202">
           <cell r="C202" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I202">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="M202">
-            <v>0</v>
+            <v>2000000</v>
           </cell>
         </row>
         <row r="203">
           <cell r="C203" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I203">
             <v>0</v>
           </cell>
           <cell r="M203">
-            <v>1168000</v>
+            <v>2500000</v>
           </cell>
         </row>
         <row r="204">
           <cell r="C204" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I204">
             <v>0</v>
           </cell>
           <cell r="M204">
-            <v>1000000</v>
+            <v>6122000</v>
           </cell>
         </row>
         <row r="205">
           <cell r="C205" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I205">
             <v>0</v>
           </cell>
           <cell r="M205">
-            <v>0</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="206">
           <cell r="C206" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I206">
             <v>0</v>
           </cell>
           <cell r="M206">
-            <v>145000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="207">
           <cell r="C207" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I207">
             <v>0</v>
           </cell>
           <cell r="M207">
-            <v>0</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="208">
           <cell r="C208" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I208">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M208">
-            <v>0</v>
+            <v>264000</v>
           </cell>
         </row>
         <row r="209">
           <cell r="C209" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I209">
             <v>0</v>
           </cell>
           <cell r="M209">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="210">
           <cell r="C210" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I210">
             <v>0</v>
           </cell>
           <cell r="M210">
-            <v>234000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="211">
           <cell r="C211" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I211">
             <v>0</v>
           </cell>
           <cell r="M211">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="212">
@@ -2824,7 +2824,7 @@
             <v>0</v>
           </cell>
           <cell r="M212">
-            <v>5905000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="213">
@@ -2835,7 +2835,7 @@
             <v>0</v>
           </cell>
           <cell r="M213">
-            <v>500000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="214">
@@ -2846,7 +2846,7 @@
             <v>0</v>
           </cell>
           <cell r="M214">
-            <v>170000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="215">
@@ -2857,18 +2857,18 @@
             <v>0</v>
           </cell>
           <cell r="M215">
-            <v>132000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="216">
           <cell r="C216" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I216">
             <v>0</v>
           </cell>
           <cell r="M216">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="217">
@@ -2879,18 +2879,18 @@
             <v>0</v>
           </cell>
           <cell r="M217">
-            <v>170000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="218">
           <cell r="C218" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I218">
             <v>0</v>
           </cell>
           <cell r="M218">
-            <v>840000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="219">
@@ -2901,18 +2901,18 @@
             <v>0</v>
           </cell>
           <cell r="M219">
-            <v>170000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="220">
           <cell r="C220" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I220">
             <v>0</v>
           </cell>
           <cell r="M220">
-            <v>0</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="221">
@@ -2920,10 +2920,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I221">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M221">
-            <v>85000</v>
+            <v>392000</v>
           </cell>
         </row>
         <row r="222">
@@ -2931,54 +2931,54 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I222">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M222">
-            <v>0</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="223">
           <cell r="C223" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I223">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M223">
-            <v>0</v>
+            <v>902000</v>
           </cell>
         </row>
         <row r="224">
           <cell r="C224" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I224">
             <v>0</v>
           </cell>
           <cell r="M224">
-            <v>0</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="225">
           <cell r="C225" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I225">
             <v>0</v>
           </cell>
           <cell r="M225">
-            <v>0</v>
+            <v>2695000</v>
           </cell>
         </row>
         <row r="226">
           <cell r="C226" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I226">
             <v>0</v>
           </cell>
           <cell r="M226">
-            <v>0</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="227">
@@ -2989,7 +2989,7 @@
             <v>0</v>
           </cell>
           <cell r="M227">
-            <v>0</v>
+            <v>1132000</v>
           </cell>
         </row>
         <row r="228">
@@ -3000,7 +3000,7 @@
             <v>0</v>
           </cell>
           <cell r="M228">
-            <v>0</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="229">
@@ -3011,7 +3011,7 @@
             <v>0</v>
           </cell>
           <cell r="M229">
-            <v>85000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="230">
@@ -3019,21 +3019,21 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I230">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M230">
-            <v>6520000</v>
+            <v>3090000</v>
           </cell>
         </row>
         <row r="231">
           <cell r="C231" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I231">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M231">
-            <v>0</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="232">
@@ -3044,7 +3044,7 @@
             <v>0</v>
           </cell>
           <cell r="M232">
-            <v>170000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="233">
@@ -3052,10 +3052,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I233">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M233">
-            <v>385000</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="234">
@@ -3063,21 +3063,21 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I234">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M234">
-            <v>132000</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="235">
           <cell r="C235" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I235">
             <v>0</v>
           </cell>
           <cell r="M235">
-            <v>0</v>
+            <v>5905000</v>
           </cell>
         </row>
         <row r="236">
@@ -3093,24 +3093,24 @@
         </row>
         <row r="237">
           <cell r="C237" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I237">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M237">
-            <v>308400</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="238">
           <cell r="C238" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I238">
             <v>0</v>
           </cell>
           <cell r="M238">
-            <v>2350000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="239">
@@ -3118,10 +3118,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I239">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M239">
-            <v>170000</v>
+            <v>1340000</v>
           </cell>
         </row>
         <row r="240">
@@ -3132,29 +3132,29 @@
             <v>0</v>
           </cell>
           <cell r="M240">
-            <v>170000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="241">
           <cell r="C241" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I241">
             <v>0</v>
           </cell>
           <cell r="M241">
-            <v>0</v>
+            <v>3255000</v>
           </cell>
         </row>
         <row r="242">
           <cell r="C242" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I242">
             <v>0</v>
           </cell>
           <cell r="M242">
-            <v>2795000</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="243">
@@ -3165,122 +3165,122 @@
             <v>0</v>
           </cell>
           <cell r="M243">
-            <v>0</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="244">
           <cell r="C244" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I244">
             <v>0</v>
           </cell>
           <cell r="M244">
-            <v>85000</v>
+            <v>291000</v>
           </cell>
         </row>
         <row r="245">
           <cell r="C245" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I245">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M245">
-            <v>0</v>
+            <v>3134000</v>
           </cell>
         </row>
         <row r="246">
           <cell r="C246" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I246">
             <v>3</v>
           </cell>
           <cell r="M246">
-            <v>308400</v>
+            <v>3295000</v>
           </cell>
         </row>
         <row r="247">
           <cell r="C247" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I247">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M247">
-            <v>132000</v>
+            <v>659000</v>
           </cell>
         </row>
         <row r="248">
           <cell r="C248" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I248">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M248">
-            <v>170000</v>
+            <v>409000</v>
           </cell>
         </row>
         <row r="249">
           <cell r="C249" t="str">
-            <v>DSE1147</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I249">
             <v>0</v>
           </cell>
           <cell r="M249">
-            <v>85000</v>
+            <v>674000</v>
           </cell>
         </row>
         <row r="250">
           <cell r="C250" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I250">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M250">
-            <v>0</v>
+            <v>3338500</v>
           </cell>
         </row>
         <row r="251">
           <cell r="C251" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I251">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M251">
-            <v>85000</v>
+            <v>258000</v>
           </cell>
         </row>
         <row r="252">
           <cell r="C252" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I252">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M252">
-            <v>0</v>
+            <v>3843000</v>
           </cell>
         </row>
         <row r="253">
           <cell r="C253" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I253">
             <v>0</v>
           </cell>
           <cell r="M253">
-            <v>300000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="254">
           <cell r="C254" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I254">
             <v>0</v>
@@ -3294,65 +3294,65 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I255">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M255">
-            <v>5813000</v>
+            <v>558000</v>
           </cell>
         </row>
         <row r="256">
           <cell r="C256" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I256">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="M256">
-            <v>0</v>
+            <v>3279200</v>
           </cell>
         </row>
         <row r="257">
           <cell r="C257" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I257">
             <v>0</v>
           </cell>
           <cell r="M257">
-            <v>0</v>
+            <v>234000</v>
           </cell>
         </row>
         <row r="258">
           <cell r="C258" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I258">
             <v>0</v>
           </cell>
           <cell r="M258">
-            <v>220800</v>
+            <v>496000</v>
           </cell>
         </row>
         <row r="259">
           <cell r="C259" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I259">
             <v>0</v>
           </cell>
           <cell r="M259">
-            <v>840000</v>
+            <v>453000</v>
           </cell>
         </row>
         <row r="260">
           <cell r="C260" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I260">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M260">
-            <v>0</v>
+            <v>522000</v>
           </cell>
         </row>
         <row r="261">
@@ -3363,84 +3363,84 @@
             <v>0</v>
           </cell>
           <cell r="M261">
-            <v>168000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="262">
           <cell r="C262" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I262">
             <v>0</v>
           </cell>
           <cell r="M262">
-            <v>170000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="263">
           <cell r="C263" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I263">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M263">
-            <v>3090000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="264">
           <cell r="C264" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I264">
             <v>0</v>
           </cell>
           <cell r="M264">
-            <v>0</v>
+            <v>324900</v>
           </cell>
         </row>
         <row r="265">
           <cell r="C265" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I265">
             <v>0</v>
           </cell>
           <cell r="M265">
-            <v>336000</v>
+            <v>302400</v>
           </cell>
         </row>
         <row r="266">
           <cell r="C266" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I266">
             <v>0</v>
           </cell>
           <cell r="M266">
-            <v>0</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="267">
           <cell r="C267" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I267">
             <v>0</v>
           </cell>
           <cell r="M267">
-            <v>85000</v>
+            <v>324900</v>
           </cell>
         </row>
         <row r="268">
           <cell r="C268" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I268">
             <v>0</v>
           </cell>
           <cell r="M268">
-            <v>3681000</v>
+            <v>2350000</v>
           </cell>
         </row>
         <row r="269">
@@ -3451,7 +3451,7 @@
             <v>0</v>
           </cell>
           <cell r="M269">
-            <v>2900000</v>
+            <v>2350000</v>
           </cell>
         </row>
         <row r="270">
@@ -3462,12 +3462,12 @@
             <v>0</v>
           </cell>
           <cell r="M270">
-            <v>0</v>
+            <v>2350000</v>
           </cell>
         </row>
         <row r="271">
           <cell r="C271" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I271">
             <v>0</v>
@@ -3481,21 +3481,21 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I272">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M272">
-            <v>2650000</v>
+            <v>824000</v>
           </cell>
         </row>
         <row r="273">
           <cell r="C273" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I273">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M273">
-            <v>0</v>
+            <v>403000</v>
           </cell>
         </row>
         <row r="274">
@@ -3503,37 +3503,37 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I274">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M274">
-            <v>3740000</v>
+            <v>2608000</v>
           </cell>
         </row>
         <row r="275">
           <cell r="C275" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I275">
             <v>0</v>
           </cell>
           <cell r="M275">
-            <v>170000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="276">
           <cell r="C276" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I276">
             <v>0</v>
           </cell>
           <cell r="M276">
-            <v>2495000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="277">
           <cell r="C277" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I277">
             <v>0</v>
@@ -3547,7 +3547,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I278">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M278">
             <v>0</v>
@@ -3555,24 +3555,24 @@
         </row>
         <row r="279">
           <cell r="C279" t="str">
-            <v>DSE1147</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I279">
             <v>0</v>
           </cell>
           <cell r="M279">
-            <v>85000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="280">
           <cell r="C280" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I280">
-            <v>6</v>
+            <v>3</v>
           </cell>
           <cell r="M280">
-            <v>630000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="281">
@@ -3580,87 +3580,87 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I281">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M281">
-            <v>3740000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="282">
           <cell r="C282" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I282">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M282">
-            <v>0</v>
+            <v>4166000</v>
           </cell>
         </row>
         <row r="283">
           <cell r="C283" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I283">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M283">
-            <v>132000</v>
+            <v>4166000</v>
           </cell>
         </row>
         <row r="284">
           <cell r="C284" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I284">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M284">
-            <v>600000</v>
+            <v>2776000</v>
           </cell>
         </row>
         <row r="285">
           <cell r="C285" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I285">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M285">
-            <v>170000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="286">
           <cell r="C286" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I286">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M286">
-            <v>170000</v>
+            <v>3616000</v>
           </cell>
         </row>
         <row r="287">
           <cell r="C287" t="str">
-            <v>DSE1082</v>
+            <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I287">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M287">
-            <v>2350000</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="288">
           <cell r="C288" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I288">
             <v>0</v>
           </cell>
           <cell r="M288">
-            <v>145000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="289">
@@ -3671,37 +3671,37 @@
             <v>0</v>
           </cell>
           <cell r="M289">
-            <v>0</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="290">
           <cell r="C290" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I290">
             <v>0</v>
           </cell>
           <cell r="M290">
-            <v>2650000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="291">
           <cell r="C291" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I291">
             <v>0</v>
           </cell>
           <cell r="M291">
-            <v>0</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="292">
           <cell r="C292" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I292">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M292">
             <v>0</v>
@@ -3709,24 +3709,24 @@
         </row>
         <row r="293">
           <cell r="C293" t="str">
-            <v>DSE1082</v>
+            <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I293">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M293">
-            <v>840000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="294">
           <cell r="C294" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I294">
             <v>0</v>
           </cell>
           <cell r="M294">
-            <v>0</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="295">
@@ -3737,7 +3737,7 @@
             <v>0</v>
           </cell>
           <cell r="M295">
-            <v>3190000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="296">
@@ -3748,18 +3748,18 @@
             <v>0</v>
           </cell>
           <cell r="M296">
-            <v>2350000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="297">
           <cell r="C297" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I297">
             <v>0</v>
           </cell>
           <cell r="M297">
-            <v>0</v>
+            <v>2000000</v>
           </cell>
         </row>
         <row r="298">
@@ -3770,7 +3770,7 @@
             <v>0</v>
           </cell>
           <cell r="M298">
-            <v>2350000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="299">
@@ -3781,7 +3781,7 @@
             <v>0</v>
           </cell>
           <cell r="M299">
-            <v>840000</v>
+            <v>2350000</v>
           </cell>
         </row>
         <row r="300">
@@ -3797,24 +3797,24 @@
         </row>
         <row r="301">
           <cell r="C301" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I301">
             <v>0</v>
           </cell>
           <cell r="M301">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="302">
           <cell r="C302" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I302">
             <v>0</v>
           </cell>
           <cell r="M302">
-            <v>1072000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="303">
@@ -3822,10 +3822,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I303">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M303">
-            <v>308400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="304">
@@ -3833,10 +3833,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I304">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M304">
-            <v>308400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="305">
@@ -3852,101 +3852,101 @@
         </row>
         <row r="306">
           <cell r="C306" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I306">
             <v>0</v>
           </cell>
           <cell r="M306">
-            <v>0</v>
+            <v>170000</v>
           </cell>
         </row>
         <row r="307">
           <cell r="C307" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I307">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M307">
-            <v>302400</v>
+            <v>422000</v>
           </cell>
         </row>
         <row r="308">
           <cell r="C308" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I308">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M308">
-            <v>522000</v>
+            <v>922000</v>
           </cell>
         </row>
         <row r="309">
           <cell r="C309" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I309">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M309">
-            <v>0</v>
+            <v>175000</v>
           </cell>
         </row>
         <row r="310">
           <cell r="C310" t="str">
-            <v>DSE-JAGOIBABNG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I310">
             <v>0</v>
           </cell>
           <cell r="M310">
-            <v>324900</v>
+            <v>85000</v>
           </cell>
         </row>
         <row r="311">
           <cell r="C311" t="str">
-            <v>DSE-BENGKAYANG01</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I311">
             <v>0</v>
           </cell>
           <cell r="M311">
-            <v>0</v>
+            <v>6520000</v>
           </cell>
         </row>
         <row r="312">
           <cell r="C312" t="str">
-            <v>DSE1082</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I312">
             <v>0</v>
           </cell>
           <cell r="M312">
-            <v>660000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="313">
           <cell r="C313" t="str">
-            <v>DSE-JAGOIBABNG02</v>
+            <v>DSE1147</v>
           </cell>
           <cell r="I313">
             <v>0</v>
           </cell>
           <cell r="M313">
-            <v>1670000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="314">
           <cell r="C314" t="str">
-            <v>DSE1147</v>
+            <v>DSE1082</v>
           </cell>
           <cell r="I314">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="M314">
-            <v>1040000</v>
+            <v>425000</v>
           </cell>
         </row>
         <row r="315">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>80905000</v>
+        <v>88623000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.13012240457750049</v>
+        <v>0.14253553996504328</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-540855720.32094395</v>
+        <v>-533137720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-30047540.017830219</v>
+        <v>-29618762.240052443</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>57322000</v>
+        <v>65846000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>9.9670141735191189E-2</v>
+        <v>0.11449147190773871</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-517795071.19165206</v>
+        <v>-509271071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-28766392.84398067</v>
+        <v>-28292837.288425114</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>21171500</v>
+        <v>24396000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.23037324956720262</v>
+        <v>0.26545997196426679</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-70729361.058193401</v>
+        <v>-67504861.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-3929408.9476774111</v>
+        <v>-3750270.0587885221</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>14152400</v>
+        <v>19994000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>5.8533082078024719E-2</v>
+        <v>8.2693426066817372E-2</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-227632236.953421</v>
+        <v>-221790636.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12646235.386301167</v>
+        <v>-12321702.052967833</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>30502900</v>
+        <v>40331600</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>6.7493257100453202E-2</v>
+        <v>8.9241057344470132E-2</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-421437061.27051902</v>
+        <v>-411608361.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-23413170.07058439</v>
+        <v>-22867131.181695502</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>1.6122070758588385E-2</v>
+        <v>7.9266847896392892E-2</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-732.32125870725895</v>
+        <v>-685.32125870725895</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-40.6845143726255</v>
+        <v>-38.073403261514386</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>9.5481921310690748E-2</v>
+        <v>0.11558337842873091</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-359.981099231874</v>
+        <v>-351.981099231874</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-19.998949957326332</v>
+        <v>-19.554505512881889</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-75</v>
+        <v>-33</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-4.166666666666667</v>
+        <v>-1.8333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.10777403985041765</v>
+        <v>0.11701181469473916</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-289.753531078332</v>
+        <v>-286.753531078332</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-16.097418393240666</v>
+        <v>-15.930751726574</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>7.777660960838946E-2</v>
+        <v>0.18064244812271102</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-367.57741493344997</v>
+        <v>-326.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-20.420967496302776</v>
+        <v>-18.143189718524997</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$D$3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$D$3</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -951,10 +951,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I42">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M42">
-            <v>0</v>
+            <v>133500</v>
           </cell>
         </row>
         <row r="43">
@@ -1237,10 +1237,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I68">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M68">
-            <v>840000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="69">
@@ -1248,10 +1248,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I69">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M69">
-            <v>425000</v>
+            <v>779000</v>
           </cell>
         </row>
         <row r="70">
@@ -1259,10 +1259,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I70">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M70">
-            <v>840000</v>
+            <v>6266000</v>
           </cell>
         </row>
         <row r="71">
@@ -1270,10 +1270,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I71">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M71">
-            <v>840000</v>
+            <v>1770000</v>
           </cell>
         </row>
         <row r="72">
@@ -1281,10 +1281,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I72">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M72">
-            <v>702000</v>
+            <v>1128000</v>
           </cell>
         </row>
         <row r="73">
@@ -1303,10 +1303,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I74">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M74">
-            <v>840000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="75">
@@ -1314,10 +1314,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I75">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M75">
-            <v>1072000</v>
+            <v>1798000</v>
           </cell>
         </row>
         <row r="76">
@@ -1325,10 +1325,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I76">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M76">
-            <v>747000</v>
+            <v>1173000</v>
           </cell>
         </row>
         <row r="77">
@@ -1336,10 +1336,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I77">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M77">
-            <v>592000</v>
+            <v>1018000</v>
           </cell>
         </row>
         <row r="78">
@@ -1372,7 +1372,7 @@
             <v>0</v>
           </cell>
           <cell r="M80">
-            <v>0</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="81">
@@ -1383,7 +1383,7 @@
             <v>0</v>
           </cell>
           <cell r="M81">
-            <v>0</v>
+            <v>52800</v>
           </cell>
         </row>
         <row r="82">
@@ -1394,7 +1394,7 @@
             <v>0</v>
           </cell>
           <cell r="M82">
-            <v>302400</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="83">
@@ -1405,7 +1405,7 @@
             <v>0</v>
           </cell>
           <cell r="M83">
-            <v>355200</v>
+            <v>408000</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,7 +1416,7 @@
             <v>0</v>
           </cell>
           <cell r="M84">
-            <v>405600</v>
+            <v>458400</v>
           </cell>
         </row>
         <row r="85">
@@ -1427,7 +1427,7 @@
             <v>0</v>
           </cell>
           <cell r="M85">
-            <v>105600</v>
+            <v>158400</v>
           </cell>
         </row>
         <row r="86">
@@ -1592,7 +1592,7 @@
             <v>0</v>
           </cell>
           <cell r="M100">
-            <v>1532800</v>
+            <v>1785600</v>
           </cell>
         </row>
         <row r="101">
@@ -1669,7 +1669,7 @@
             <v>0</v>
           </cell>
           <cell r="M107">
-            <v>170400</v>
+            <v>223200</v>
           </cell>
         </row>
         <row r="108">
@@ -1713,7 +1713,7 @@
             <v>0</v>
           </cell>
           <cell r="M111">
-            <v>302400</v>
+            <v>368400</v>
           </cell>
         </row>
         <row r="112">
@@ -1746,7 +1746,7 @@
             <v>3</v>
           </cell>
           <cell r="M114">
-            <v>370800</v>
+            <v>1370800</v>
           </cell>
         </row>
         <row r="115">
@@ -1757,7 +1757,7 @@
             <v>0</v>
           </cell>
           <cell r="M115">
-            <v>355200</v>
+            <v>408000</v>
           </cell>
         </row>
         <row r="116">
@@ -1768,7 +1768,7 @@
             <v>0</v>
           </cell>
           <cell r="M116">
-            <v>302400</v>
+            <v>394800</v>
           </cell>
         </row>
         <row r="117">
@@ -1801,7 +1801,7 @@
             <v>0</v>
           </cell>
           <cell r="M119">
-            <v>302400</v>
+            <v>855200</v>
           </cell>
         </row>
         <row r="120">
@@ -1900,7 +1900,7 @@
             <v>0</v>
           </cell>
           <cell r="M128">
-            <v>302400</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="129">
@@ -1941,10 +1941,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="M132">
-            <v>2770000</v>
+            <v>3770000</v>
           </cell>
         </row>
         <row r="133">
@@ -1966,7 +1966,7 @@
             <v>0</v>
           </cell>
           <cell r="M134">
-            <v>0</v>
+            <v>224400</v>
           </cell>
         </row>
         <row r="135">
@@ -2032,7 +2032,7 @@
             <v>0</v>
           </cell>
           <cell r="M140">
-            <v>417000</v>
+            <v>617000</v>
           </cell>
         </row>
         <row r="141">
@@ -2241,7 +2241,7 @@
             <v>0</v>
           </cell>
           <cell r="M159">
-            <v>761500</v>
+            <v>1261500</v>
           </cell>
         </row>
         <row r="160">
@@ -2285,7 +2285,7 @@
             <v>0</v>
           </cell>
           <cell r="M163">
-            <v>1670000</v>
+            <v>2670000</v>
           </cell>
         </row>
         <row r="164">
@@ -2461,7 +2461,7 @@
             <v>3</v>
           </cell>
           <cell r="M179">
-            <v>692000</v>
+            <v>1160000</v>
           </cell>
         </row>
         <row r="180">
@@ -2472,7 +2472,7 @@
             <v>2</v>
           </cell>
           <cell r="M180">
-            <v>1000000</v>
+            <v>2000000</v>
           </cell>
         </row>
         <row r="181">
@@ -2483,7 +2483,7 @@
             <v>0</v>
           </cell>
           <cell r="M181">
-            <v>170000</v>
+            <v>404000</v>
           </cell>
         </row>
         <row r="182">
@@ -2494,7 +2494,7 @@
             <v>0</v>
           </cell>
           <cell r="M182">
-            <v>85000</v>
+            <v>217000</v>
           </cell>
         </row>
         <row r="183">
@@ -2505,7 +2505,7 @@
             <v>0</v>
           </cell>
           <cell r="M183">
-            <v>432000</v>
+            <v>564000</v>
           </cell>
         </row>
         <row r="184">
@@ -2516,7 +2516,7 @@
             <v>3</v>
           </cell>
           <cell r="M184">
-            <v>2354000</v>
+            <v>2854000</v>
           </cell>
         </row>
         <row r="185">
@@ -2538,7 +2538,7 @@
             <v>0</v>
           </cell>
           <cell r="M186">
-            <v>170000</v>
+            <v>536000</v>
           </cell>
         </row>
         <row r="187">
@@ -2549,7 +2549,7 @@
             <v>0</v>
           </cell>
           <cell r="M187">
-            <v>3320000</v>
+            <v>5320000</v>
           </cell>
         </row>
         <row r="188">
@@ -2571,7 +2571,7 @@
             <v>0</v>
           </cell>
           <cell r="M189">
-            <v>170000</v>
+            <v>536000</v>
           </cell>
         </row>
         <row r="190">
@@ -3173,10 +3173,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I244">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M244">
-            <v>291000</v>
+            <v>381000</v>
           </cell>
         </row>
         <row r="245">
@@ -3195,10 +3195,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I246">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M246">
-            <v>3295000</v>
+            <v>3385000</v>
           </cell>
         </row>
         <row r="247">
@@ -3217,10 +3217,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I248">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M248">
-            <v>409000</v>
+            <v>499000</v>
           </cell>
         </row>
         <row r="249">
@@ -3228,10 +3228,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I249">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M249">
-            <v>674000</v>
+            <v>964000</v>
           </cell>
         </row>
         <row r="250">
@@ -3239,10 +3239,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I250">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M250">
-            <v>3338500</v>
+            <v>3428500</v>
           </cell>
         </row>
         <row r="251">
@@ -3261,10 +3261,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I252">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M252">
-            <v>3843000</v>
+            <v>3933000</v>
           </cell>
         </row>
         <row r="253">
@@ -3319,7 +3319,7 @@
             <v>0</v>
           </cell>
           <cell r="M257">
-            <v>234000</v>
+            <v>351000</v>
           </cell>
         </row>
         <row r="258">
@@ -3330,7 +3330,7 @@
             <v>0</v>
           </cell>
           <cell r="M258">
-            <v>496000</v>
+            <v>566000</v>
           </cell>
         </row>
         <row r="259">
@@ -3418,7 +3418,7 @@
             <v>0</v>
           </cell>
           <cell r="M266">
-            <v>300000</v>
+            <v>600000</v>
           </cell>
         </row>
         <row r="267">
@@ -3484,7 +3484,7 @@
             <v>3</v>
           </cell>
           <cell r="M272">
-            <v>824000</v>
+            <v>1052000</v>
           </cell>
         </row>
         <row r="273">
@@ -3723,10 +3723,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I294">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M294">
-            <v>840000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="295">
@@ -3734,10 +3734,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I295">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M295">
-            <v>840000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="296">
@@ -3745,10 +3745,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I296">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M296">
-            <v>840000</v>
+            <v>1266000</v>
           </cell>
         </row>
         <row r="297">
@@ -3847,7 +3847,7 @@
             <v>0</v>
           </cell>
           <cell r="M305">
-            <v>85000</v>
+            <v>349000</v>
           </cell>
         </row>
         <row r="306">
@@ -3858,7 +3858,7 @@
             <v>0</v>
           </cell>
           <cell r="M306">
-            <v>170000</v>
+            <v>302000</v>
           </cell>
         </row>
         <row r="307">
@@ -3869,7 +3869,7 @@
             <v>3</v>
           </cell>
           <cell r="M307">
-            <v>422000</v>
+            <v>656000</v>
           </cell>
         </row>
         <row r="308">
@@ -3880,7 +3880,7 @@
             <v>3</v>
           </cell>
           <cell r="M308">
-            <v>922000</v>
+            <v>1156000</v>
           </cell>
         </row>
         <row r="309">
@@ -3891,7 +3891,7 @@
             <v>3</v>
           </cell>
           <cell r="M309">
-            <v>175000</v>
+            <v>643000</v>
           </cell>
         </row>
         <row r="310">
@@ -3902,7 +3902,7 @@
             <v>0</v>
           </cell>
           <cell r="M310">
-            <v>85000</v>
+            <v>319000</v>
           </cell>
         </row>
         <row r="311">
@@ -3913,7 +3913,7 @@
             <v>0</v>
           </cell>
           <cell r="M311">
-            <v>6520000</v>
+            <v>6754000</v>
           </cell>
         </row>
         <row r="312">
@@ -3943,10 +3943,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I314">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M314">
-            <v>425000</v>
+            <v>851000</v>
           </cell>
         </row>
         <row r="315">
@@ -3954,14 +3954,14 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I315">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M315">
-            <v>0</v>
+            <v>626000</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>88623000</v>
+        <v>100747000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.14253553996504328</v>
+        <v>0.16203500270650073</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-533137720.32094395</v>
+        <v>-521013720.32094395</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-29618762.240052443</v>
+        <v>-28945206.684496887</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>65846000</v>
+        <v>72844000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.11449147190773871</v>
+        <v>0.1266594292690113</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-509271071.19165206</v>
+        <v>-502273071.19165206</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-28292837.288425114</v>
+        <v>-27904059.510647338</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>24396000</v>
+        <v>25269500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.26545997196426679</v>
+        <v>0.27496477953562226</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-67504861.058193401</v>
+        <v>-66631361.058193401</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-3750270.0587885221</v>
+        <v>-3701742.2810107446</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>19994000</v>
+        <v>21957600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>8.2693426066817372E-2</v>
+        <v>9.0814703021143806E-2</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-221790636.953421</v>
+        <v>-219827036.953421</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12321702.052967833</v>
+        <v>-12212613.164078943</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>40331600</v>
+        <v>44218600</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>8.9241057344470132E-2</v>
+        <v>9.7841757289375747E-2</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-411608361.27051902</v>
+        <v>-407721361.27051902</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-22867131.181695502</v>
+        <v>-22651186.737251058</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>7.9266847896392892E-2</v>
+        <v>0.13569409555145223</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-685.32125870725895</v>
+        <v>-643.32125870725895</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-38.073403261514386</v>
+        <v>-35.74006992818105</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0.56000000000000005</v>
+        <v>0.84</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-33</v>
+        <v>-12</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-1.8333333333333333</v>
+        <v>-0.66666666666666663</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.18064244812271102</v>
+        <v>0.18315137101330423</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-326.57741493344997</v>
+        <v>-325.57741493344997</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-18.143189718524997</v>
+        <v>-18.087634162969444</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -4280,7 +4280,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="10">
-        <v>621760720.32094395</v>
+        <v>445042813.60751247</v>
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.16203500270650073</v>
+        <v>0.22637597309648896</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-521013720.32094395</v>
+        <v>-344295813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-28945206.684496887</v>
+        <v>-19127545.200417358</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="10">
-        <v>575117071.19165206</v>
+        <v>448406502.2821191</v>
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
@@ -4315,15 +4315,15 @@
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.1266594292690113</v>
+        <v>0.16245081110391554</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-502273071.19165206</v>
+        <v>-375562502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-27904059.510647338</v>
+        <v>-20864583.460117728</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4334,7 +4334,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="10">
-        <v>91900861.058193401</v>
+        <v>162679175.99138665</v>
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
@@ -4342,15 +4342,15 @@
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.27496477953562226</v>
+        <v>0.15533334150486439</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-66631361.058193401</v>
+        <v>-137409675.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-3701742.2810107446</v>
+        <v>-7633870.8884103699</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4361,7 +4361,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="10">
-        <v>241784636.953421</v>
+        <v>259026973.39112824</v>
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
@@ -4369,15 +4369,15 @@
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>9.0814703021143806E-2</v>
+        <v>8.4769550107216957E-2</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-219827036.953421</v>
+        <v>-237069373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12212613.164078943</v>
+        <v>-13170520.743951568</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4388,7 +4388,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="10">
-        <v>451939961.27051902</v>
+        <v>386163597.57738662</v>
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
@@ -4396,15 +4396,15 @@
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>9.7841757289375747E-2</v>
+        <v>0.11450742710448945</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-407721361.27051902</v>
+        <v>-341944997.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-22651186.737251058</v>
+        <v>-18996944.309854813</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4441,7 +4441,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="10">
-        <v>744.32125870725895</v>
+        <v>756.93438881757243</v>
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
@@ -4449,15 +4449,15 @@
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.13569409555145223</v>
+        <v>0.13343296525049525</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-643.32125870725895</v>
+        <v>-655.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-35.74006992818105</v>
+        <v>-36.440799378754022</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4468,7 +4468,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="10">
-        <v>397.981099231874</v>
+        <v>437.17700755954917</v>
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
@@ -4476,15 +4476,15 @@
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.11558337842873091</v>
+        <v>0.10522053814491651</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-351.981099231874</v>
+        <v>-391.17700755954917</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-19.554505512881889</v>
+        <v>-21.73205597553051</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4495,7 +4495,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="10">
-        <v>75</v>
+        <v>226.71387819141353</v>
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
@@ -4503,15 +4503,15 @@
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0.84</v>
+        <v>0.27788329723162947</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-12</v>
+        <v>-163.71387819141353</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-0.66666666666666663</v>
+        <v>-9.0952154550785291</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4522,7 +4522,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="10">
-        <v>324.753531078332</v>
+        <v>394.79760376551121</v>
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
@@ -4530,15 +4530,15 @@
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.11701181469473916</v>
+        <v>9.6251850663637714E-2</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-286.753531078332</v>
+        <v>-356.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-15.930751726574</v>
+        <v>-19.822089098083957</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4549,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="10">
-        <v>398.57741493344997</v>
+        <v>418.3771216659535</v>
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
@@ -4557,15 +4557,15 @@
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.18315137101330423</v>
+        <v>0.17448372824335667</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-325.57741493344997</v>
+        <v>-345.3771216659535</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-18.087634162969444</v>
+        <v>-19.187617870330751</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -558,7 +558,7 @@
             <v>0</v>
           </cell>
           <cell r="M6">
-            <v>0</v>
+            <v>58000</v>
           </cell>
         </row>
         <row r="7">
@@ -613,7 +613,7 @@
             <v>3</v>
           </cell>
           <cell r="M11">
-            <v>90000</v>
+            <v>148000</v>
           </cell>
         </row>
         <row r="12">
@@ -635,7 +635,7 @@
             <v>0</v>
           </cell>
           <cell r="M13">
-            <v>0</v>
+            <v>58000</v>
           </cell>
         </row>
         <row r="14">
@@ -646,7 +646,7 @@
             <v>3</v>
           </cell>
           <cell r="M14">
-            <v>90000</v>
+            <v>148000</v>
           </cell>
         </row>
         <row r="15">
@@ -764,10 +764,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I25">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M25">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="26">
@@ -775,10 +775,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I26">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M26">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="27">
@@ -797,10 +797,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I28">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M28">
-            <v>1000000</v>
+            <v>1120000</v>
           </cell>
         </row>
         <row r="29">
@@ -819,10 +819,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I30">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M30">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="31">
@@ -844,7 +844,7 @@
             <v>0</v>
           </cell>
           <cell r="M32">
-            <v>0</v>
+            <v>58000</v>
           </cell>
         </row>
         <row r="33">
@@ -863,10 +863,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I34">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M34">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="35">
@@ -874,10 +874,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I35">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M35">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="36">
@@ -940,10 +940,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I41">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M41">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="42">
@@ -1119,7 +1119,7 @@
             <v>0</v>
           </cell>
           <cell r="M57">
-            <v>0</v>
+            <v>385000</v>
           </cell>
         </row>
         <row r="58">
@@ -1130,7 +1130,7 @@
             <v>0</v>
           </cell>
           <cell r="M58">
-            <v>840000</v>
+            <v>1008000</v>
           </cell>
         </row>
         <row r="59">
@@ -1152,7 +1152,7 @@
             <v>0</v>
           </cell>
           <cell r="M60">
-            <v>660000</v>
+            <v>1045000</v>
           </cell>
         </row>
         <row r="61">
@@ -1163,7 +1163,7 @@
             <v>0</v>
           </cell>
           <cell r="M61">
-            <v>660000</v>
+            <v>1045000</v>
           </cell>
         </row>
         <row r="62">
@@ -1174,7 +1174,7 @@
             <v>0</v>
           </cell>
           <cell r="M62">
-            <v>3526000</v>
+            <v>3911000</v>
           </cell>
         </row>
         <row r="63">
@@ -1185,7 +1185,7 @@
             <v>0</v>
           </cell>
           <cell r="M63">
-            <v>3190000</v>
+            <v>3575000</v>
           </cell>
         </row>
         <row r="64">
@@ -1196,7 +1196,7 @@
             <v>0</v>
           </cell>
           <cell r="M64">
-            <v>660000</v>
+            <v>996000</v>
           </cell>
         </row>
         <row r="65">
@@ -1204,10 +1204,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I65">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M65">
-            <v>5000000</v>
+            <v>5475000</v>
           </cell>
         </row>
         <row r="66">
@@ -1218,7 +1218,7 @@
             <v>0</v>
           </cell>
           <cell r="M66">
-            <v>2795000</v>
+            <v>3180000</v>
           </cell>
         </row>
         <row r="67">
@@ -1229,7 +1229,7 @@
             <v>0</v>
           </cell>
           <cell r="M67">
-            <v>660000</v>
+            <v>1045000</v>
           </cell>
         </row>
         <row r="68">
@@ -1361,7 +1361,7 @@
             <v>0</v>
           </cell>
           <cell r="M79">
-            <v>168000</v>
+            <v>285000</v>
           </cell>
         </row>
         <row r="80">
@@ -1438,7 +1438,7 @@
             <v>0</v>
           </cell>
           <cell r="M86">
-            <v>1700800</v>
+            <v>2000800</v>
           </cell>
         </row>
         <row r="87">
@@ -1592,7 +1592,7 @@
             <v>0</v>
           </cell>
           <cell r="M100">
-            <v>1785600</v>
+            <v>2038400</v>
           </cell>
         </row>
         <row r="101">
@@ -1625,7 +1625,7 @@
             <v>2</v>
           </cell>
           <cell r="M103">
-            <v>52800</v>
+            <v>1052800</v>
           </cell>
         </row>
         <row r="104">
@@ -1647,7 +1647,7 @@
             <v>3</v>
           </cell>
           <cell r="M105">
-            <v>2285500</v>
+            <v>2402500</v>
           </cell>
         </row>
         <row r="106">
@@ -1724,7 +1724,7 @@
             <v>3</v>
           </cell>
           <cell r="M112">
-            <v>378000</v>
+            <v>430800</v>
           </cell>
         </row>
         <row r="113">
@@ -1735,7 +1735,7 @@
             <v>3</v>
           </cell>
           <cell r="M113">
-            <v>578000</v>
+            <v>680800</v>
           </cell>
         </row>
         <row r="114">
@@ -1746,7 +1746,7 @@
             <v>3</v>
           </cell>
           <cell r="M114">
-            <v>1370800</v>
+            <v>1511200</v>
           </cell>
         </row>
         <row r="115">
@@ -1776,7 +1776,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I117">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M117">
             <v>658400</v>
@@ -1823,7 +1823,7 @@
             <v>3</v>
           </cell>
           <cell r="M121">
-            <v>325200</v>
+            <v>378000</v>
           </cell>
         </row>
         <row r="122">
@@ -1834,7 +1834,7 @@
             <v>3</v>
           </cell>
           <cell r="M122">
-            <v>971500</v>
+            <v>1088500</v>
           </cell>
         </row>
         <row r="123">
@@ -1845,7 +1845,7 @@
             <v>3</v>
           </cell>
           <cell r="M123">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="124">
@@ -1856,7 +1856,7 @@
             <v>3</v>
           </cell>
           <cell r="M124">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="125">
@@ -1867,7 +1867,7 @@
             <v>5</v>
           </cell>
           <cell r="M125">
-            <v>325200</v>
+            <v>378000</v>
           </cell>
         </row>
         <row r="126">
@@ -1878,7 +1878,7 @@
             <v>0</v>
           </cell>
           <cell r="M126">
-            <v>489200</v>
+            <v>989200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>0</v>
           </cell>
           <cell r="M127">
-            <v>3251800</v>
+            <v>3368800</v>
           </cell>
         </row>
         <row r="128">
@@ -1911,7 +1911,7 @@
             <v>9</v>
           </cell>
           <cell r="M129">
-            <v>1429900</v>
+            <v>1546900</v>
           </cell>
         </row>
         <row r="130">
@@ -1977,7 +1977,7 @@
             <v>3</v>
           </cell>
           <cell r="M135">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="137">
@@ -1999,7 +1999,7 @@
             <v>3</v>
           </cell>
           <cell r="M137">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="138">
@@ -2043,7 +2043,7 @@
             <v>3</v>
           </cell>
           <cell r="M141">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="142">
@@ -2065,7 +2065,7 @@
             <v>3</v>
           </cell>
           <cell r="M143">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
         </row>
         <row r="144">
@@ -2252,7 +2252,7 @@
             <v>0</v>
           </cell>
           <cell r="M160">
-            <v>1313000</v>
+            <v>2313000</v>
           </cell>
         </row>
         <row r="161">
@@ -2340,7 +2340,7 @@
             <v>0</v>
           </cell>
           <cell r="M168">
-            <v>217000</v>
+            <v>517000</v>
           </cell>
         </row>
         <row r="169">
@@ -2362,7 +2362,7 @@
             <v>0</v>
           </cell>
           <cell r="M170">
-            <v>950000</v>
+            <v>1100000</v>
           </cell>
         </row>
         <row r="171">
@@ -2923,7 +2923,7 @@
             <v>3</v>
           </cell>
           <cell r="M221">
-            <v>392000</v>
+            <v>794000</v>
           </cell>
         </row>
         <row r="222">
@@ -2934,7 +2934,7 @@
             <v>3</v>
           </cell>
           <cell r="M222">
-            <v>1090000</v>
+            <v>1324000</v>
           </cell>
         </row>
         <row r="223">
@@ -2945,7 +2945,7 @@
             <v>1</v>
           </cell>
           <cell r="M223">
-            <v>902000</v>
+            <v>1002000</v>
           </cell>
         </row>
         <row r="224">
@@ -2956,7 +2956,7 @@
             <v>0</v>
           </cell>
           <cell r="M224">
-            <v>85000</v>
+            <v>319000</v>
           </cell>
         </row>
         <row r="225">
@@ -2978,7 +2978,7 @@
             <v>0</v>
           </cell>
           <cell r="M226">
-            <v>85000</v>
+            <v>487000</v>
           </cell>
         </row>
         <row r="227">
@@ -3022,7 +3022,7 @@
             <v>3</v>
           </cell>
           <cell r="M230">
-            <v>3090000</v>
+            <v>6090000</v>
           </cell>
         </row>
         <row r="231">
@@ -3033,7 +3033,7 @@
             <v>1</v>
           </cell>
           <cell r="M231">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="232">
@@ -3044,7 +3044,7 @@
             <v>0</v>
           </cell>
           <cell r="M232">
-            <v>85000</v>
+            <v>319000</v>
           </cell>
         </row>
         <row r="233">
@@ -3055,7 +3055,7 @@
             <v>3</v>
           </cell>
           <cell r="M233">
-            <v>90000</v>
+            <v>3135000</v>
           </cell>
         </row>
         <row r="234">
@@ -3066,7 +3066,7 @@
             <v>3</v>
           </cell>
           <cell r="M234">
-            <v>90000</v>
+            <v>524000</v>
           </cell>
         </row>
         <row r="235">
@@ -3077,7 +3077,7 @@
             <v>0</v>
           </cell>
           <cell r="M235">
-            <v>5905000</v>
+            <v>6139000</v>
           </cell>
         </row>
         <row r="236">
@@ -3088,7 +3088,7 @@
             <v>0</v>
           </cell>
           <cell r="M236">
-            <v>0</v>
+            <v>402000</v>
           </cell>
         </row>
         <row r="237">
@@ -3099,7 +3099,7 @@
             <v>0</v>
           </cell>
           <cell r="M237">
-            <v>85000</v>
+            <v>319000</v>
           </cell>
         </row>
         <row r="238">
@@ -3110,7 +3110,7 @@
             <v>0</v>
           </cell>
           <cell r="M238">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="239">
@@ -3132,7 +3132,7 @@
             <v>0</v>
           </cell>
           <cell r="M240">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="241">
@@ -3143,7 +3143,7 @@
             <v>0</v>
           </cell>
           <cell r="M241">
-            <v>3255000</v>
+            <v>3657000</v>
           </cell>
         </row>
         <row r="242">
@@ -3154,7 +3154,7 @@
             <v>0</v>
           </cell>
           <cell r="M242">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="243">
@@ -3165,7 +3165,7 @@
             <v>0</v>
           </cell>
           <cell r="M243">
-            <v>85000</v>
+            <v>487000</v>
           </cell>
         </row>
         <row r="244">
@@ -3195,10 +3195,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I246">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M246">
-            <v>3385000</v>
+            <v>3475000</v>
           </cell>
         </row>
         <row r="247">
@@ -3217,10 +3217,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I248">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M248">
-            <v>499000</v>
+            <v>589000</v>
           </cell>
         </row>
         <row r="249">
@@ -3228,10 +3228,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I249">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M249">
-            <v>964000</v>
+            <v>1054000</v>
           </cell>
         </row>
         <row r="250">
@@ -3239,10 +3239,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I250">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M250">
-            <v>3428500</v>
+            <v>3518500</v>
           </cell>
         </row>
         <row r="251">
@@ -3253,7 +3253,7 @@
             <v>3</v>
           </cell>
           <cell r="M251">
-            <v>258000</v>
+            <v>288000</v>
           </cell>
         </row>
         <row r="252">
@@ -3261,10 +3261,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I252">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M252">
-            <v>3933000</v>
+            <v>4023000</v>
           </cell>
         </row>
         <row r="253">
@@ -3297,7 +3297,7 @@
             <v>3</v>
           </cell>
           <cell r="M255">
-            <v>558000</v>
+            <v>658000</v>
           </cell>
         </row>
         <row r="256">
@@ -3308,7 +3308,7 @@
             <v>8</v>
           </cell>
           <cell r="M256">
-            <v>3279200</v>
+            <v>3396200</v>
           </cell>
         </row>
         <row r="257">
@@ -3341,7 +3341,7 @@
             <v>0</v>
           </cell>
           <cell r="M259">
-            <v>453000</v>
+            <v>570000</v>
           </cell>
         </row>
         <row r="260">
@@ -3363,7 +3363,7 @@
             <v>0</v>
           </cell>
           <cell r="M261">
-            <v>302400</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="262">
@@ -3374,7 +3374,7 @@
             <v>0</v>
           </cell>
           <cell r="M262">
-            <v>302400</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="263">
@@ -3385,7 +3385,7 @@
             <v>0</v>
           </cell>
           <cell r="M263">
-            <v>302400</v>
+            <v>355200</v>
           </cell>
         </row>
         <row r="264">
@@ -3484,7 +3484,7 @@
             <v>3</v>
           </cell>
           <cell r="M272">
-            <v>1052000</v>
+            <v>1218000</v>
           </cell>
         </row>
         <row r="273">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>100747000</v>
+        <v>104617000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.22637597309648896</v>
+        <v>0.23507176568468924</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-344295813.60751247</v>
+        <v>-340425813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-19127545.200417358</v>
+        <v>-18912545.200417358</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>72844000</v>
+        <v>83725000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.16245081110391554</v>
+        <v>0.18671673932891286</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-375562502.2821191</v>
+        <v>-364681502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-20864583.460117728</v>
+        <v>-20260083.460117728</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>25269500</v>
+        <v>26669500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.15533334150486439</v>
+        <v>0.16393923707489191</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-137409675.99138665</v>
+        <v>-136009675.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7633870.8884103699</v>
+        <v>-7556093.1106325919</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>21957600</v>
+        <v>23999600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>8.4769550107216957E-2</v>
+        <v>9.2652898985005838E-2</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-237069373.39112824</v>
+        <v>-235027373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-13170520.743951568</v>
+        <v>-13057076.299507124</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>44218600</v>
+        <v>47078000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.11450742710448945</v>
+        <v>0.12191206083469749</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-341944997.57738662</v>
+        <v>-339085597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18996944.309854813</v>
+        <v>-18838088.754299257</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.13343296525049525</v>
+        <v>0.13739632065397531</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-655.93438881757243</v>
+        <v>-652.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-36.440799378754022</v>
+        <v>-36.274132712087358</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0.27788329723162947</v>
+        <v>0.44108459878036421</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-163.71387819141353</v>
+        <v>-126.71387819141353</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-9.0952154550785291</v>
+        <v>-7.0396598995229738</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>9.6251850663637714E-2</v>
+        <v>9.8784794102154502E-2</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-356.79760376551121</v>
+        <v>-355.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-19.822089098083957</v>
+        <v>-19.7665335425284</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
